--- a/utils/usuarios/USUARIOS_GERENCIAS.xlsx
+++ b/utils/usuarios/USUARIOS_GERENCIAS.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://misiontecnologicasac-my.sharepoint.com/personal/rodrigo_carbonel_misiontecnologica_com/Documents/Documentos/MT-Code/InformeRicoPollo/rico-pollo/utils/usuarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38C1207D-583A-4E3A-B5BC-FBDCA7AC70E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{38C1207D-583A-4E3A-B5BC-FBDCA7AC70E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A3079A1-AD83-496E-B6C3-B2641DFFAF99}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD6E822C-CF80-4DA1-BFD3-8180C150640C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="USUARIOS" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -8388,7 +8388,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.28515625" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="50.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.140625" customWidth="1"/>
     <col min="8" max="8" width="11.42578125" customWidth="1"/>

--- a/utils/usuarios/USUARIOS_GERENCIAS.xlsx
+++ b/utils/usuarios/USUARIOS_GERENCIAS.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://misiontecnologicasac-my.sharepoint.com/personal/rodrigo_carbonel_misiontecnologica_com/Documents/Documentos/MT-Code/InformeRicoPollo/rico-pollo/utils/usuarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{38C1207D-583A-4E3A-B5BC-FBDCA7AC70E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A3079A1-AD83-496E-B6C3-B2641DFFAF99}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="8_{38C1207D-583A-4E3A-B5BC-FBDCA7AC70E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D15C2AD-0CD7-4B04-91F0-67FEEDA38CA5}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD6E822C-CF80-4DA1-BFD3-8180C150640C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD6E822C-CF80-4DA1-BFD3-8180C150640C}"/>
   </bookViews>
   <sheets>
     <sheet name="USUARIOS" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6803" uniqueCount="2650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6879" uniqueCount="2664">
   <si>
     <t>Nombres</t>
   </si>
@@ -7989,6 +7989,48 @@
   </si>
   <si>
     <t>ramaestro2</t>
+  </si>
+  <si>
+    <t>MCACERES@PRINTSERVER3</t>
+  </si>
+  <si>
+    <t>gzevallos</t>
+  </si>
+  <si>
+    <t>Gianmarco Andre Zevallos Guzman</t>
+  </si>
+  <si>
+    <t>victor.begazo</t>
+  </si>
+  <si>
+    <t>Victor Alfonso Begazo Flores</t>
+  </si>
+  <si>
+    <t>GERENCIA LAS BRAVAS</t>
+  </si>
+  <si>
+    <t>SoniaGutierrezLuque</t>
+  </si>
+  <si>
+    <t>arosas</t>
+  </si>
+  <si>
+    <t>calidad.cusco</t>
+  </si>
+  <si>
+    <t>DESPACHO-23$</t>
+  </si>
+  <si>
+    <t>Jose Manuel Chavez Hinojosa</t>
+  </si>
+  <si>
+    <t>jchavezh</t>
+  </si>
+  <si>
+    <t>LORDONEZ@PRINTSERVER3</t>
+  </si>
+  <si>
+    <t>COORDINADOR DE PROYECTOS</t>
   </si>
 </sst>
 </file>
@@ -8044,8 +8086,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{517BEBB2-3A02-4480-8F49-0C1B6B8E7CC2}" name="Tabla1" displayName="Tabla1" ref="A1:O529" totalsRowShown="0">
-  <autoFilter ref="A1:O529" xr:uid="{517BEBB2-3A02-4480-8F49-0C1B6B8E7CC2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{517BEBB2-3A02-4480-8F49-0C1B6B8E7CC2}" name="Tabla1" displayName="Tabla1" ref="A1:O538" totalsRowShown="0">
+  <autoFilter ref="A1:O538" xr:uid="{517BEBB2-3A02-4480-8F49-0C1B6B8E7CC2}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{1F8AA320-CA47-4CCC-8454-28538F97A9FB}" name="Nombres"/>
     <tableColumn id="2" xr3:uid="{DA26F0AB-497D-4C16-8E65-60FDC2ACE02E}" name="Correo"/>
@@ -8384,7 +8426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DD67B1C-CBCD-4893-AAAA-7508CBFE6155}">
-  <dimension ref="A1:O529"/>
+  <dimension ref="A1:O538"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.140625" bestFit="1" customWidth="1"/>
@@ -28612,66 +28654,66 @@
     </row>
     <row r="431" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B431" t="s">
-        <v>2454</v>
+        <v>2452</v>
       </c>
       <c r="C431" t="s">
-        <v>866</v>
+        <v>2659</v>
       </c>
       <c r="D431" t="s">
-        <v>2455</v>
+        <v>1896</v>
       </c>
       <c r="E431">
-        <v>29615064</v>
+        <v>40380181</v>
       </c>
       <c r="F431" t="s">
         <v>947</v>
       </c>
       <c r="G431" t="s">
-        <v>1094</v>
+        <v>1234</v>
       </c>
       <c r="H431">
-        <v>1050101</v>
+        <v>506020101</v>
       </c>
       <c r="I431" t="s">
-        <v>1314</v>
+        <v>1235</v>
       </c>
       <c r="J431" t="s">
         <v>1087</v>
       </c>
       <c r="K431" t="s">
-        <v>950</v>
+        <v>1102</v>
       </c>
       <c r="L431" t="s">
-        <v>1315</v>
+        <v>1173</v>
       </c>
       <c r="M431" t="s">
-        <v>1315</v>
+        <v>1236</v>
       </c>
       <c r="N431" t="s">
-        <v>1315</v>
+        <v>1237</v>
       </c>
       <c r="O431" t="s">
-        <v>2456</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="432" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B432" t="s">
-        <v>2457</v>
+        <v>2454</v>
       </c>
       <c r="C432" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="D432" t="s">
-        <v>1249</v>
+        <v>2455</v>
       </c>
       <c r="E432">
-        <v>72470007</v>
+        <v>29615064</v>
       </c>
       <c r="F432" t="s">
         <v>947</v>
@@ -28680,10 +28722,10 @@
         <v>1094</v>
       </c>
       <c r="H432">
-        <v>1050201</v>
+        <v>1050101</v>
       </c>
       <c r="I432" t="s">
-        <v>1120</v>
+        <v>1314</v>
       </c>
       <c r="J432" t="s">
         <v>1087</v>
@@ -28692,33 +28734,33 @@
         <v>950</v>
       </c>
       <c r="L432" t="s">
-        <v>1121</v>
+        <v>1315</v>
       </c>
       <c r="M432" t="s">
-        <v>1122</v>
+        <v>1315</v>
       </c>
       <c r="N432" t="s">
-        <v>1122</v>
+        <v>1315</v>
       </c>
       <c r="O432" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="433" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B433" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
       <c r="C433" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="D433" t="s">
-        <v>2030</v>
+        <v>1249</v>
       </c>
       <c r="E433">
-        <v>71074522</v>
+        <v>72470007</v>
       </c>
       <c r="F433" t="s">
         <v>947</v>
@@ -28727,10 +28769,10 @@
         <v>1094</v>
       </c>
       <c r="H433">
-        <v>1030405</v>
+        <v>1050201</v>
       </c>
       <c r="I433" t="s">
-        <v>2031</v>
+        <v>1120</v>
       </c>
       <c r="J433" t="s">
         <v>1087</v>
@@ -28739,127 +28781,127 @@
         <v>950</v>
       </c>
       <c r="L433" t="s">
-        <v>950</v>
+        <v>1121</v>
       </c>
       <c r="M433" t="s">
-        <v>1261</v>
+        <v>1122</v>
       </c>
       <c r="N433" t="s">
-        <v>2032</v>
+        <v>1122</v>
       </c>
       <c r="O433" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="434" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B434" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
       <c r="C434" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="D434" t="s">
-        <v>1125</v>
+        <v>2030</v>
       </c>
       <c r="E434">
-        <v>47013715</v>
+        <v>71074522</v>
       </c>
       <c r="F434" t="s">
         <v>947</v>
       </c>
       <c r="G434" t="s">
-        <v>1126</v>
+        <v>1094</v>
       </c>
       <c r="H434">
-        <v>201010117</v>
+        <v>1030405</v>
       </c>
       <c r="I434" t="s">
-        <v>1146</v>
+        <v>2031</v>
       </c>
       <c r="J434" t="s">
         <v>1087</v>
       </c>
       <c r="K434" t="s">
-        <v>1128</v>
+        <v>950</v>
       </c>
       <c r="L434" t="s">
-        <v>1128</v>
+        <v>950</v>
       </c>
       <c r="M434" t="s">
-        <v>1147</v>
+        <v>1261</v>
       </c>
       <c r="N434" t="s">
-        <v>1148</v>
+        <v>2032</v>
       </c>
       <c r="O434" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="435" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B435" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
       <c r="C435" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D435" t="s">
-        <v>2464</v>
+        <v>1125</v>
       </c>
       <c r="E435">
-        <v>42620385</v>
+        <v>47013715</v>
       </c>
       <c r="F435" t="s">
         <v>947</v>
       </c>
       <c r="G435" t="s">
-        <v>1094</v>
+        <v>1126</v>
       </c>
       <c r="H435">
-        <v>105040902</v>
+        <v>201010117</v>
       </c>
       <c r="I435" t="s">
-        <v>1301</v>
+        <v>1146</v>
       </c>
       <c r="J435" t="s">
         <v>1087</v>
       </c>
       <c r="K435" t="s">
-        <v>1183</v>
+        <v>1128</v>
       </c>
       <c r="L435" t="s">
-        <v>1302</v>
+        <v>1128</v>
       </c>
       <c r="M435" t="s">
-        <v>1303</v>
+        <v>1147</v>
       </c>
       <c r="N435" t="s">
-        <v>1303</v>
+        <v>1148</v>
       </c>
       <c r="O435" t="s">
-        <v>2465</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="436" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B436" t="s">
-        <v>2466</v>
+        <v>2463</v>
       </c>
       <c r="C436" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="D436" t="s">
-        <v>1577</v>
+        <v>2464</v>
       </c>
       <c r="E436">
-        <v>30962925</v>
+        <v>42620385</v>
       </c>
       <c r="F436" t="s">
         <v>947</v>
@@ -28868,45 +28910,45 @@
         <v>1094</v>
       </c>
       <c r="H436">
-        <v>10503</v>
+        <v>105040902</v>
       </c>
       <c r="I436" t="s">
-        <v>1224</v>
+        <v>1301</v>
       </c>
       <c r="J436" t="s">
         <v>1087</v>
       </c>
       <c r="K436" t="s">
-        <v>950</v>
+        <v>1183</v>
       </c>
       <c r="L436" t="s">
-        <v>1121</v>
+        <v>1302</v>
       </c>
       <c r="M436" t="s">
-        <v>1225</v>
+        <v>1303</v>
       </c>
       <c r="N436" t="s">
-        <v>1225</v>
+        <v>1303</v>
       </c>
       <c r="O436" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="437" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B437" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
       <c r="C437" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="D437" t="s">
-        <v>2469</v>
+        <v>1577</v>
       </c>
       <c r="E437">
-        <v>77013365</v>
+        <v>30962925</v>
       </c>
       <c r="F437" t="s">
         <v>947</v>
@@ -28915,327 +28957,327 @@
         <v>1094</v>
       </c>
       <c r="H437">
-        <v>1030906</v>
+        <v>10503</v>
       </c>
       <c r="I437" t="s">
-        <v>1807</v>
+        <v>1224</v>
       </c>
       <c r="J437" t="s">
         <v>1087</v>
       </c>
       <c r="K437" t="s">
-        <v>1166</v>
+        <v>950</v>
       </c>
       <c r="L437" t="s">
-        <v>1808</v>
+        <v>1121</v>
       </c>
       <c r="M437" t="s">
-        <v>1808</v>
+        <v>1225</v>
       </c>
       <c r="N437" t="s">
-        <v>1808</v>
+        <v>1225</v>
       </c>
       <c r="O437" t="s">
-        <v>2470</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="438" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B438" t="s">
-        <v>2471</v>
+        <v>2468</v>
       </c>
       <c r="C438" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D438" t="s">
-        <v>2472</v>
+        <v>2469</v>
       </c>
       <c r="E438">
-        <v>42150781</v>
+        <v>77013365</v>
       </c>
       <c r="F438" t="s">
         <v>947</v>
       </c>
       <c r="G438" t="s">
-        <v>1580</v>
+        <v>1094</v>
       </c>
       <c r="H438">
-        <v>4020403</v>
+        <v>1030906</v>
       </c>
       <c r="I438" t="s">
-        <v>1581</v>
+        <v>1807</v>
       </c>
       <c r="J438" t="s">
         <v>1087</v>
       </c>
       <c r="K438" t="s">
-        <v>1088</v>
+        <v>1166</v>
       </c>
       <c r="L438" t="s">
-        <v>1582</v>
+        <v>1808</v>
       </c>
       <c r="M438" t="s">
-        <v>1582</v>
+        <v>1808</v>
       </c>
       <c r="N438" t="s">
-        <v>1582</v>
+        <v>1808</v>
       </c>
       <c r="O438" t="s">
-        <v>2473</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="439" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B439" t="s">
-        <v>2474</v>
+        <v>2471</v>
       </c>
       <c r="C439" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="D439" t="s">
-        <v>1252</v>
+        <v>2472</v>
       </c>
       <c r="E439">
-        <v>70365451</v>
+        <v>42150781</v>
       </c>
       <c r="F439" t="s">
         <v>947</v>
       </c>
       <c r="G439" t="s">
-        <v>1703</v>
+        <v>1580</v>
       </c>
       <c r="H439">
-        <v>3050102</v>
+        <v>4020403</v>
       </c>
       <c r="I439" t="s">
-        <v>1704</v>
+        <v>1581</v>
       </c>
       <c r="J439" t="s">
         <v>1087</v>
       </c>
       <c r="K439" t="s">
-        <v>1114</v>
+        <v>1088</v>
       </c>
       <c r="L439" t="s">
-        <v>1705</v>
+        <v>1582</v>
       </c>
       <c r="M439" t="s">
-        <v>1705</v>
+        <v>1582</v>
       </c>
       <c r="N439" t="s">
-        <v>1705</v>
+        <v>1582</v>
       </c>
       <c r="O439" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="440" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B440" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="C440" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="D440" t="s">
-        <v>2341</v>
+        <v>1252</v>
       </c>
       <c r="E440">
-        <v>74415225</v>
+        <v>70365451</v>
       </c>
       <c r="F440" t="s">
         <v>947</v>
       </c>
       <c r="G440" t="s">
-        <v>1094</v>
+        <v>1703</v>
       </c>
       <c r="H440">
-        <v>1030901</v>
+        <v>3050102</v>
       </c>
       <c r="I440" t="s">
-        <v>1325</v>
+        <v>1704</v>
       </c>
       <c r="J440" t="s">
         <v>1087</v>
       </c>
       <c r="K440" t="s">
-        <v>1166</v>
+        <v>1114</v>
       </c>
       <c r="L440" t="s">
-        <v>1326</v>
+        <v>1705</v>
       </c>
       <c r="M440" t="s">
-        <v>1327</v>
+        <v>1705</v>
       </c>
       <c r="N440" t="s">
-        <v>1327</v>
+        <v>1705</v>
       </c>
       <c r="O440" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="441" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B441" t="s">
-        <v>2478</v>
+        <v>2476</v>
       </c>
       <c r="C441" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="D441" t="s">
-        <v>1125</v>
+        <v>2341</v>
       </c>
       <c r="E441">
-        <v>80249490</v>
+        <v>74415225</v>
       </c>
       <c r="F441" t="s">
         <v>947</v>
       </c>
       <c r="G441" t="s">
-        <v>1126</v>
+        <v>1094</v>
       </c>
       <c r="H441">
-        <v>201010112</v>
+        <v>1030901</v>
       </c>
       <c r="I441" t="s">
-        <v>1723</v>
+        <v>1325</v>
       </c>
       <c r="J441" t="s">
         <v>1087</v>
       </c>
       <c r="K441" t="s">
-        <v>1128</v>
+        <v>1166</v>
       </c>
       <c r="L441" t="s">
-        <v>1129</v>
+        <v>1326</v>
       </c>
       <c r="M441" t="s">
-        <v>1130</v>
+        <v>1327</v>
       </c>
       <c r="N441" t="s">
-        <v>1131</v>
+        <v>1327</v>
       </c>
       <c r="O441" t="s">
-        <v>2479</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="442" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B442" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="C442" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D442" t="s">
-        <v>2481</v>
+        <v>1125</v>
       </c>
       <c r="E442">
-        <v>42835288</v>
+        <v>80249490</v>
       </c>
       <c r="F442" t="s">
         <v>947</v>
       </c>
       <c r="G442" t="s">
-        <v>1703</v>
+        <v>1126</v>
       </c>
       <c r="H442">
-        <v>3050102</v>
+        <v>201010112</v>
       </c>
       <c r="I442" t="s">
-        <v>1704</v>
+        <v>1723</v>
       </c>
       <c r="J442" t="s">
         <v>1087</v>
       </c>
       <c r="K442" t="s">
-        <v>1114</v>
+        <v>1128</v>
       </c>
       <c r="L442" t="s">
-        <v>1705</v>
+        <v>1129</v>
       </c>
       <c r="M442" t="s">
-        <v>1705</v>
+        <v>1130</v>
       </c>
       <c r="N442" t="s">
-        <v>1705</v>
+        <v>1131</v>
       </c>
       <c r="O442" t="s">
-        <v>2482</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="443" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B443" t="s">
-        <v>2483</v>
+        <v>2480</v>
       </c>
       <c r="C443" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D443" t="s">
-        <v>2484</v>
+        <v>2481</v>
       </c>
       <c r="E443">
-        <v>42337420</v>
+        <v>42835288</v>
       </c>
       <c r="F443" t="s">
         <v>947</v>
       </c>
       <c r="G443" t="s">
-        <v>1094</v>
+        <v>1703</v>
       </c>
       <c r="H443">
-        <v>105040910</v>
+        <v>3050102</v>
       </c>
       <c r="I443" t="s">
-        <v>2363</v>
+        <v>1704</v>
       </c>
       <c r="J443" t="s">
         <v>1087</v>
       </c>
       <c r="K443" t="s">
-        <v>1183</v>
+        <v>1114</v>
       </c>
       <c r="L443" t="s">
-        <v>1206</v>
+        <v>1705</v>
       </c>
       <c r="M443" t="s">
-        <v>2417</v>
+        <v>1705</v>
       </c>
       <c r="N443" t="s">
-        <v>2417</v>
+        <v>1705</v>
       </c>
       <c r="O443" t="s">
-        <v>2485</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="444" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B444" t="s">
-        <v>2486</v>
+        <v>2483</v>
       </c>
       <c r="C444" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D444" t="s">
-        <v>2487</v>
+        <v>2484</v>
       </c>
       <c r="E444">
-        <v>74656140</v>
+        <v>42337420</v>
       </c>
       <c r="F444" t="s">
         <v>947</v>
@@ -29244,45 +29286,45 @@
         <v>1094</v>
       </c>
       <c r="H444">
-        <v>20703</v>
+        <v>105040910</v>
       </c>
       <c r="I444" t="s">
-        <v>1689</v>
+        <v>2363</v>
       </c>
       <c r="J444" t="s">
         <v>1087</v>
       </c>
       <c r="K444" t="s">
-        <v>1128</v>
+        <v>1183</v>
       </c>
       <c r="L444" t="s">
-        <v>1192</v>
+        <v>1206</v>
       </c>
       <c r="M444" t="s">
-        <v>1192</v>
+        <v>2417</v>
       </c>
       <c r="N444" t="s">
-        <v>1192</v>
+        <v>2417</v>
       </c>
       <c r="O444" t="s">
-        <v>2488</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="445" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B445" t="s">
-        <v>2489</v>
+        <v>2486</v>
       </c>
       <c r="C445" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D445" t="s">
-        <v>2490</v>
+        <v>2487</v>
       </c>
       <c r="E445">
-        <v>46477187</v>
+        <v>74656140</v>
       </c>
       <c r="F445" t="s">
         <v>947</v>
@@ -29291,186 +29333,186 @@
         <v>1094</v>
       </c>
       <c r="H445">
-        <v>105040904</v>
+        <v>20703</v>
       </c>
       <c r="I445" t="s">
-        <v>1680</v>
+        <v>1689</v>
       </c>
       <c r="J445" t="s">
         <v>1087</v>
       </c>
       <c r="K445" t="s">
-        <v>1183</v>
+        <v>1128</v>
       </c>
       <c r="L445" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
       <c r="M445" t="s">
-        <v>2062</v>
+        <v>1192</v>
       </c>
       <c r="N445" t="s">
-        <v>2062</v>
+        <v>1192</v>
       </c>
       <c r="O445" t="s">
-        <v>2491</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="446" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B446" t="s">
-        <v>2492</v>
+        <v>2489</v>
       </c>
       <c r="C446" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="D446" t="s">
-        <v>1228</v>
+        <v>2490</v>
       </c>
       <c r="E446">
-        <v>29596002</v>
+        <v>46477187</v>
       </c>
       <c r="F446" t="s">
         <v>947</v>
       </c>
       <c r="G446" t="s">
-        <v>1211</v>
+        <v>1094</v>
       </c>
       <c r="H446">
-        <v>30220</v>
+        <v>105040904</v>
       </c>
       <c r="I446" t="s">
-        <v>1212</v>
+        <v>1680</v>
       </c>
       <c r="J446" t="s">
         <v>1087</v>
       </c>
       <c r="K446" t="s">
-        <v>1102</v>
+        <v>1183</v>
       </c>
       <c r="L446" t="s">
-        <v>1173</v>
+        <v>1184</v>
       </c>
       <c r="M446" t="s">
-        <v>1213</v>
+        <v>2062</v>
       </c>
       <c r="N446" t="s">
-        <v>1213</v>
+        <v>2062</v>
       </c>
       <c r="O446" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="447" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B447" t="s">
-        <v>2494</v>
+        <v>2492</v>
       </c>
       <c r="C447" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="D447" t="s">
-        <v>1359</v>
+        <v>1228</v>
       </c>
       <c r="E447">
-        <v>78551157</v>
+        <v>29596002</v>
       </c>
       <c r="F447" t="s">
         <v>947</v>
       </c>
       <c r="G447" t="s">
-        <v>1113</v>
+        <v>1211</v>
       </c>
       <c r="H447">
-        <v>5010102</v>
+        <v>30220</v>
       </c>
       <c r="I447" t="s">
-        <v>982</v>
+        <v>1212</v>
       </c>
       <c r="J447" t="s">
         <v>1087</v>
       </c>
       <c r="K447" t="s">
-        <v>1114</v>
+        <v>1102</v>
       </c>
       <c r="L447" t="s">
-        <v>1115</v>
+        <v>1173</v>
       </c>
       <c r="M447" t="s">
-        <v>1115</v>
+        <v>1213</v>
       </c>
       <c r="N447" t="s">
-        <v>1115</v>
+        <v>1213</v>
       </c>
       <c r="O447" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="448" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B448" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
       <c r="C448" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="D448" t="s">
-        <v>2189</v>
+        <v>1359</v>
       </c>
       <c r="E448">
-        <v>43531468</v>
+        <v>78551157</v>
       </c>
       <c r="F448" t="s">
         <v>947</v>
       </c>
       <c r="G448" t="s">
-        <v>1094</v>
+        <v>1113</v>
       </c>
       <c r="H448">
-        <v>10505</v>
+        <v>5010102</v>
       </c>
       <c r="I448" t="s">
-        <v>1095</v>
+        <v>982</v>
       </c>
       <c r="J448" t="s">
         <v>1087</v>
       </c>
       <c r="K448" t="s">
-        <v>950</v>
+        <v>1114</v>
       </c>
       <c r="L448" t="s">
-        <v>1096</v>
+        <v>1115</v>
       </c>
       <c r="M448" t="s">
-        <v>1096</v>
+        <v>1115</v>
       </c>
       <c r="N448" t="s">
-        <v>1096</v>
+        <v>1115</v>
       </c>
       <c r="O448" t="s">
-        <v>2497</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="449" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B449" t="s">
-        <v>2498</v>
+        <v>2496</v>
       </c>
       <c r="C449" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="D449" t="s">
         <v>2189</v>
       </c>
       <c r="E449">
-        <v>71521175</v>
+        <v>43531468</v>
       </c>
       <c r="F449" t="s">
         <v>947</v>
@@ -29479,10 +29521,10 @@
         <v>1094</v>
       </c>
       <c r="H449">
-        <v>10316</v>
+        <v>10505</v>
       </c>
       <c r="I449" t="s">
-        <v>1662</v>
+        <v>1095</v>
       </c>
       <c r="J449" t="s">
         <v>1087</v>
@@ -29494,30 +29536,30 @@
         <v>1096</v>
       </c>
       <c r="M449" t="s">
-        <v>1663</v>
+        <v>1096</v>
       </c>
       <c r="N449" t="s">
-        <v>1663</v>
+        <v>1096</v>
       </c>
       <c r="O449" t="s">
-        <v>2499</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="450" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B450" t="s">
-        <v>2500</v>
+        <v>2498</v>
       </c>
       <c r="C450" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="D450" t="s">
-        <v>2120</v>
+        <v>2189</v>
       </c>
       <c r="E450">
-        <v>70007698</v>
+        <v>71521175</v>
       </c>
       <c r="F450" t="s">
         <v>947</v>
@@ -29526,280 +29568,280 @@
         <v>1094</v>
       </c>
       <c r="H450">
-        <v>10108</v>
+        <v>10316</v>
       </c>
       <c r="I450" t="s">
-        <v>1107</v>
+        <v>1662</v>
       </c>
       <c r="J450" t="s">
-        <v>1108</v>
+        <v>1087</v>
       </c>
       <c r="K450" t="s">
-        <v>1109</v>
+        <v>950</v>
       </c>
       <c r="L450" t="s">
-        <v>1109</v>
+        <v>1096</v>
       </c>
       <c r="M450" t="s">
-        <v>1109</v>
+        <v>1663</v>
       </c>
       <c r="N450" t="s">
-        <v>1109</v>
-      </c>
-      <c r="O450">
-        <v>7698</v>
+        <v>1663</v>
+      </c>
+      <c r="O450" t="s">
+        <v>2499</v>
       </c>
     </row>
     <row r="451" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B451" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="C451" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="D451" t="s">
-        <v>2502</v>
+        <v>2120</v>
       </c>
       <c r="E451">
-        <v>41972588</v>
+        <v>70007698</v>
       </c>
       <c r="F451" t="s">
-        <v>1424</v>
+        <v>947</v>
       </c>
       <c r="G451" t="s">
-        <v>2020</v>
+        <v>1094</v>
       </c>
       <c r="H451">
-        <v>1050206</v>
+        <v>10108</v>
       </c>
       <c r="I451" t="s">
-        <v>2503</v>
+        <v>1107</v>
       </c>
       <c r="J451" t="s">
-        <v>1087</v>
+        <v>1108</v>
       </c>
       <c r="K451" t="s">
-        <v>950</v>
+        <v>1109</v>
       </c>
       <c r="L451" t="s">
-        <v>1121</v>
+        <v>1109</v>
       </c>
       <c r="M451" t="s">
-        <v>1122</v>
+        <v>1109</v>
       </c>
       <c r="N451" t="s">
-        <v>1122</v>
-      </c>
-      <c r="O451" t="s">
-        <v>2504</v>
+        <v>1109</v>
+      </c>
+      <c r="O451">
+        <v>7698</v>
       </c>
     </row>
     <row r="452" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B452" t="s">
-        <v>2505</v>
+        <v>2501</v>
       </c>
       <c r="C452" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="D452" t="s">
-        <v>1297</v>
+        <v>2502</v>
       </c>
       <c r="E452">
-        <v>61839935</v>
+        <v>41972588</v>
       </c>
       <c r="F452" t="s">
-        <v>947</v>
+        <v>1424</v>
       </c>
       <c r="G452" t="s">
-        <v>1094</v>
+        <v>2020</v>
       </c>
       <c r="H452">
-        <v>5230101</v>
+        <v>1050206</v>
       </c>
       <c r="I452" t="s">
-        <v>1245</v>
+        <v>2503</v>
       </c>
       <c r="J452" t="s">
         <v>1087</v>
       </c>
       <c r="K452" t="s">
-        <v>1160</v>
+        <v>950</v>
       </c>
       <c r="L452" t="s">
-        <v>1160</v>
+        <v>1121</v>
       </c>
       <c r="M452" t="s">
-        <v>1160</v>
+        <v>1122</v>
       </c>
       <c r="N452" t="s">
-        <v>1160</v>
+        <v>1122</v>
       </c>
       <c r="O452" t="s">
-        <v>2506</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="453" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B453" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="C453" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D453" t="s">
-        <v>1218</v>
+        <v>1297</v>
       </c>
       <c r="E453">
-        <v>46886990</v>
+        <v>61839935</v>
       </c>
       <c r="F453" t="s">
         <v>947</v>
       </c>
       <c r="G453" t="s">
-        <v>1135</v>
+        <v>1094</v>
       </c>
       <c r="H453">
-        <v>4030403</v>
+        <v>5230101</v>
       </c>
       <c r="I453" t="s">
-        <v>2508</v>
+        <v>1245</v>
       </c>
       <c r="J453" t="s">
         <v>1087</v>
       </c>
       <c r="K453" t="s">
-        <v>1137</v>
+        <v>1160</v>
       </c>
       <c r="L453" t="s">
-        <v>1220</v>
+        <v>1160</v>
       </c>
       <c r="M453" t="s">
-        <v>1220</v>
+        <v>1160</v>
       </c>
       <c r="N453" t="s">
-        <v>1220</v>
+        <v>1160</v>
       </c>
       <c r="O453" t="s">
-        <v>2509</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="454" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B454" t="s">
-        <v>2510</v>
+        <v>2507</v>
       </c>
       <c r="C454" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D454" t="s">
-        <v>2511</v>
+        <v>1218</v>
       </c>
       <c r="E454">
-        <v>43017511</v>
+        <v>46886990</v>
       </c>
       <c r="F454" t="s">
-        <v>1897</v>
+        <v>947</v>
       </c>
       <c r="G454" t="s">
-        <v>2512</v>
+        <v>1135</v>
       </c>
       <c r="H454">
-        <v>2020104</v>
+        <v>4030403</v>
       </c>
       <c r="I454" t="s">
-        <v>2513</v>
+        <v>2508</v>
       </c>
       <c r="J454" t="s">
         <v>1087</v>
       </c>
       <c r="K454" t="s">
-        <v>1102</v>
+        <v>1137</v>
       </c>
       <c r="L454" t="s">
-        <v>1173</v>
+        <v>1220</v>
       </c>
       <c r="M454" t="s">
-        <v>2514</v>
+        <v>1220</v>
       </c>
       <c r="N454" t="s">
-        <v>2514</v>
+        <v>1220</v>
       </c>
       <c r="O454" t="s">
-        <v>2515</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="455" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B455" t="s">
-        <v>2516</v>
+        <v>2510</v>
       </c>
       <c r="C455" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="D455" t="s">
-        <v>1119</v>
+        <v>2511</v>
       </c>
       <c r="E455">
-        <v>72518779</v>
+        <v>43017511</v>
       </c>
       <c r="F455" t="s">
-        <v>947</v>
+        <v>1897</v>
       </c>
       <c r="G455" t="s">
-        <v>1094</v>
+        <v>2512</v>
       </c>
       <c r="H455">
-        <v>1050201</v>
+        <v>2020104</v>
       </c>
       <c r="I455" t="s">
-        <v>1120</v>
+        <v>2513</v>
       </c>
       <c r="J455" t="s">
         <v>1087</v>
       </c>
       <c r="K455" t="s">
-        <v>950</v>
+        <v>1102</v>
       </c>
       <c r="L455" t="s">
-        <v>1121</v>
+        <v>1173</v>
       </c>
       <c r="M455" t="s">
-        <v>1122</v>
+        <v>2514</v>
       </c>
       <c r="N455" t="s">
-        <v>1122</v>
+        <v>2514</v>
       </c>
       <c r="O455" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="456" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B456" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
       <c r="C456" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="D456" t="s">
-        <v>2189</v>
+        <v>1119</v>
       </c>
       <c r="E456">
-        <v>72086016</v>
+        <v>72518779</v>
       </c>
       <c r="F456" t="s">
         <v>947</v>
@@ -29808,10 +29850,10 @@
         <v>1094</v>
       </c>
       <c r="H456">
-        <v>10505</v>
+        <v>1050201</v>
       </c>
       <c r="I456" t="s">
-        <v>1095</v>
+        <v>1120</v>
       </c>
       <c r="J456" t="s">
         <v>1087</v>
@@ -29820,33 +29862,33 @@
         <v>950</v>
       </c>
       <c r="L456" t="s">
-        <v>1096</v>
+        <v>1121</v>
       </c>
       <c r="M456" t="s">
-        <v>1096</v>
+        <v>1122</v>
       </c>
       <c r="N456" t="s">
-        <v>1096</v>
+        <v>1122</v>
       </c>
       <c r="O456" t="s">
-        <v>2519</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="457" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B457" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="C457" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D457" t="s">
-        <v>2521</v>
+        <v>2189</v>
       </c>
       <c r="E457">
-        <v>42095716</v>
+        <v>72086016</v>
       </c>
       <c r="F457" t="s">
         <v>947</v>
@@ -29855,45 +29897,45 @@
         <v>1094</v>
       </c>
       <c r="H457">
-        <v>52303</v>
+        <v>10505</v>
       </c>
       <c r="I457" t="s">
-        <v>2229</v>
+        <v>1095</v>
       </c>
       <c r="J457" t="s">
         <v>1087</v>
       </c>
       <c r="K457" t="s">
-        <v>1160</v>
+        <v>950</v>
       </c>
       <c r="L457" t="s">
-        <v>1160</v>
+        <v>1096</v>
       </c>
       <c r="M457" t="s">
-        <v>2230</v>
+        <v>1096</v>
       </c>
       <c r="N457" t="s">
-        <v>2230</v>
+        <v>1096</v>
       </c>
       <c r="O457" t="s">
-        <v>2522</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="458" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>313</v>
+        <v>917</v>
       </c>
       <c r="B458" t="s">
-        <v>2523</v>
+        <v>2520</v>
       </c>
       <c r="C458" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D458" t="s">
-        <v>920</v>
+        <v>2521</v>
       </c>
       <c r="E458">
-        <v>30834746</v>
+        <v>42095716</v>
       </c>
       <c r="F458" t="s">
         <v>947</v>
@@ -29902,139 +29944,139 @@
         <v>1094</v>
       </c>
       <c r="H458">
-        <v>20703</v>
+        <v>52303</v>
       </c>
       <c r="I458" t="s">
-        <v>1689</v>
+        <v>2229</v>
       </c>
       <c r="J458" t="s">
-        <v>1108</v>
+        <v>1087</v>
       </c>
       <c r="K458" t="s">
-        <v>1128</v>
+        <v>1160</v>
       </c>
       <c r="L458" t="s">
-        <v>1192</v>
+        <v>1160</v>
       </c>
       <c r="M458" t="s">
-        <v>1193</v>
+        <v>2230</v>
       </c>
       <c r="N458" t="s">
-        <v>1193</v>
+        <v>2230</v>
       </c>
       <c r="O458" t="s">
-        <v>1690</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="459" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>921</v>
+        <v>313</v>
       </c>
       <c r="B459" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="C459" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="D459" t="s">
-        <v>923</v>
-      </c>
-      <c r="E459" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F459" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G459" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H459" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I459" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J459" t="e">
-        <v>#N/A</v>
+        <v>920</v>
+      </c>
+      <c r="E459">
+        <v>30834746</v>
+      </c>
+      <c r="F459" t="s">
+        <v>947</v>
+      </c>
+      <c r="G459" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H459">
+        <v>20703</v>
+      </c>
+      <c r="I459" t="s">
+        <v>1689</v>
+      </c>
+      <c r="J459" t="s">
+        <v>1108</v>
       </c>
       <c r="K459" t="s">
-        <v>1114</v>
+        <v>1128</v>
       </c>
       <c r="L459" t="s">
-        <v>1383</v>
+        <v>1192</v>
       </c>
       <c r="M459" t="s">
-        <v>1420</v>
+        <v>1193</v>
       </c>
       <c r="N459" t="s">
-        <v>1420</v>
+        <v>1193</v>
       </c>
       <c r="O459" t="s">
-        <v>1849</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="460" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="B460" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="C460" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="D460" t="s">
-        <v>953</v>
-      </c>
-      <c r="E460">
-        <v>47013717</v>
-      </c>
-      <c r="F460" t="s">
-        <v>947</v>
-      </c>
-      <c r="G460" t="s">
-        <v>1094</v>
-      </c>
-      <c r="H460">
-        <v>1031201</v>
-      </c>
-      <c r="I460" t="s">
-        <v>956</v>
-      </c>
-      <c r="J460" t="s">
-        <v>1087</v>
+        <v>923</v>
+      </c>
+      <c r="E460" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F460" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G460" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H460" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I460" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J460" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K460" t="s">
-        <v>1183</v>
+        <v>1114</v>
       </c>
       <c r="L460" t="s">
-        <v>1290</v>
+        <v>1383</v>
       </c>
       <c r="M460" t="s">
-        <v>1445</v>
+        <v>1420</v>
       </c>
       <c r="N460" t="s">
-        <v>1445</v>
+        <v>1420</v>
       </c>
       <c r="O460" t="s">
-        <v>926</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="461" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="B461" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="C461" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="D461" t="s">
-        <v>2527</v>
+        <v>953</v>
       </c>
       <c r="E461">
-        <v>72699844</v>
+        <v>47013717</v>
       </c>
       <c r="F461" t="s">
         <v>947</v>
@@ -30043,45 +30085,45 @@
         <v>1094</v>
       </c>
       <c r="H461">
-        <v>1030902</v>
+        <v>1031201</v>
       </c>
       <c r="I461" t="s">
-        <v>1165</v>
+        <v>956</v>
       </c>
       <c r="J461" t="s">
         <v>1087</v>
       </c>
       <c r="K461" t="s">
-        <v>1166</v>
+        <v>1183</v>
       </c>
       <c r="L461" t="s">
-        <v>1167</v>
+        <v>1290</v>
       </c>
       <c r="M461" t="s">
-        <v>1168</v>
+        <v>1445</v>
       </c>
       <c r="N461" t="s">
-        <v>1168</v>
-      </c>
-      <c r="O461">
-        <v>726998</v>
+        <v>1445</v>
+      </c>
+      <c r="O461" t="s">
+        <v>926</v>
       </c>
     </row>
     <row r="462" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B462" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
       <c r="C462" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="D462" t="s">
-        <v>1277</v>
+        <v>2527</v>
       </c>
       <c r="E462">
-        <v>71992166</v>
+        <v>72699844</v>
       </c>
       <c r="F462" t="s">
         <v>947</v>
@@ -30090,92 +30132,92 @@
         <v>1094</v>
       </c>
       <c r="H462">
-        <v>1030401</v>
+        <v>1030902</v>
       </c>
       <c r="I462" t="s">
-        <v>1260</v>
+        <v>1165</v>
       </c>
       <c r="J462" t="s">
         <v>1087</v>
       </c>
       <c r="K462" t="s">
-        <v>950</v>
+        <v>1166</v>
       </c>
       <c r="L462" t="s">
-        <v>950</v>
+        <v>1167</v>
       </c>
       <c r="M462" t="s">
-        <v>1261</v>
+        <v>1168</v>
       </c>
       <c r="N462" t="s">
-        <v>1261</v>
+        <v>1168</v>
       </c>
       <c r="O462">
-        <v>719921</v>
+        <v>726998</v>
       </c>
     </row>
     <row r="463" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B463" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="C463" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="D463" t="s">
-        <v>1512</v>
+        <v>1277</v>
       </c>
       <c r="E463">
-        <v>42863492</v>
+        <v>71992166</v>
       </c>
       <c r="F463" t="s">
         <v>947</v>
       </c>
       <c r="G463" t="s">
-        <v>1234</v>
+        <v>1094</v>
       </c>
       <c r="H463">
-        <v>506020202</v>
+        <v>1030401</v>
       </c>
       <c r="I463" t="s">
-        <v>1513</v>
+        <v>1260</v>
       </c>
       <c r="J463" t="s">
         <v>1087</v>
       </c>
       <c r="K463" t="s">
-        <v>1102</v>
+        <v>950</v>
       </c>
       <c r="L463" t="s">
-        <v>1173</v>
+        <v>950</v>
       </c>
       <c r="M463" t="s">
-        <v>1514</v>
+        <v>1261</v>
       </c>
       <c r="N463" t="s">
-        <v>1515</v>
+        <v>1261</v>
       </c>
       <c r="O463">
-        <v>428634</v>
+        <v>719921</v>
       </c>
     </row>
     <row r="464" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B464" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="C464" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="D464" t="s">
         <v>1512</v>
       </c>
       <c r="E464">
-        <v>29728577</v>
+        <v>42863492</v>
       </c>
       <c r="F464" t="s">
         <v>947</v>
@@ -30205,24 +30247,24 @@
         <v>1515</v>
       </c>
       <c r="O464">
-        <v>297285</v>
+        <v>428634</v>
       </c>
     </row>
     <row r="465" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B465" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="C465" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="D465" t="s">
         <v>1512</v>
       </c>
       <c r="E465">
-        <v>41647191</v>
+        <v>29728577</v>
       </c>
       <c r="F465" t="s">
         <v>947</v>
@@ -30252,24 +30294,24 @@
         <v>1515</v>
       </c>
       <c r="O465">
-        <v>416471</v>
+        <v>297285</v>
       </c>
     </row>
     <row r="466" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B466" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="C466" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="D466" t="s">
         <v>1512</v>
       </c>
       <c r="E466">
-        <v>48396508</v>
+        <v>41647191</v>
       </c>
       <c r="F466" t="s">
         <v>947</v>
@@ -30299,24 +30341,24 @@
         <v>1515</v>
       </c>
       <c r="O466">
-        <v>483965</v>
+        <v>416471</v>
       </c>
     </row>
     <row r="467" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B467" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="C467" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="D467" t="s">
         <v>1512</v>
       </c>
       <c r="E467">
-        <v>46948495</v>
+        <v>48396508</v>
       </c>
       <c r="F467" t="s">
         <v>947</v>
@@ -30346,54 +30388,54 @@
         <v>1515</v>
       </c>
       <c r="O467">
-        <v>469484</v>
+        <v>483965</v>
       </c>
     </row>
     <row r="468" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B468" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="C468" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="D468" t="s">
-        <v>2535</v>
+        <v>1512</v>
       </c>
       <c r="E468">
-        <v>25856172</v>
+        <v>46948495</v>
       </c>
       <c r="F468" t="s">
         <v>947</v>
       </c>
       <c r="G468" t="s">
-        <v>1094</v>
+        <v>1234</v>
       </c>
       <c r="H468">
-        <v>1030902</v>
+        <v>506020202</v>
       </c>
       <c r="I468" t="s">
-        <v>1165</v>
+        <v>1513</v>
       </c>
       <c r="J468" t="s">
         <v>1087</v>
       </c>
       <c r="K468" t="s">
-        <v>1166</v>
+        <v>1102</v>
       </c>
       <c r="L468" t="s">
-        <v>1167</v>
+        <v>1173</v>
       </c>
       <c r="M468" t="s">
-        <v>1256</v>
+        <v>1514</v>
       </c>
       <c r="N468" t="s">
-        <v>1256</v>
+        <v>1515</v>
       </c>
       <c r="O468">
-        <v>258561</v>
+        <v>469484</v>
       </c>
     </row>
     <row r="469" spans="1:15" x14ac:dyDescent="0.25">
@@ -30404,7 +30446,7 @@
         <v>2534</v>
       </c>
       <c r="C469" t="s">
-        <v>2649</v>
+        <v>942</v>
       </c>
       <c r="D469" t="s">
         <v>2535</v>
@@ -30445,66 +30487,66 @@
     </row>
     <row r="470" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="B470" t="s">
-        <v>2536</v>
+        <v>2534</v>
       </c>
       <c r="C470" t="s">
-        <v>944</v>
+        <v>2649</v>
       </c>
       <c r="D470" t="s">
-        <v>945</v>
-      </c>
-      <c r="E470" t="s">
-        <v>946</v>
+        <v>2535</v>
+      </c>
+      <c r="E470">
+        <v>25856172</v>
       </c>
       <c r="F470" t="s">
         <v>947</v>
       </c>
-      <c r="G470" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H470" t="s">
-        <v>948</v>
+      <c r="G470" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H470">
+        <v>1030902</v>
       </c>
       <c r="I470" t="s">
-        <v>949</v>
-      </c>
-      <c r="J470" t="e">
-        <v>#N/A</v>
+        <v>1165</v>
+      </c>
+      <c r="J470" t="s">
+        <v>1087</v>
       </c>
       <c r="K470" t="s">
-        <v>950</v>
-      </c>
-      <c r="L470" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M470" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N470" t="e">
-        <v>#N/A</v>
+        <v>1166</v>
+      </c>
+      <c r="L470" t="s">
+        <v>1167</v>
+      </c>
+      <c r="M470" t="s">
+        <v>1256</v>
+      </c>
+      <c r="N470" t="s">
+        <v>1256</v>
       </c>
       <c r="O470">
-        <v>757054</v>
+        <v>258561</v>
       </c>
     </row>
     <row r="471" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="B471" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="C471" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="D471" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="E471" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="F471" t="s">
         <v>947</v>
@@ -30513,16 +30555,16 @@
         <v>#N/A</v>
       </c>
       <c r="H471" t="s">
-        <v>955</v>
+        <v>948</v>
       </c>
       <c r="I471" t="s">
-        <v>956</v>
+        <v>949</v>
       </c>
       <c r="J471" t="e">
         <v>#N/A</v>
       </c>
       <c r="K471" t="s">
-        <v>1183</v>
+        <v>950</v>
       </c>
       <c r="L471" t="e">
         <v>#N/A</v>
@@ -30534,133 +30576,133 @@
         <v>#N/A</v>
       </c>
       <c r="O471">
-        <v>734894</v>
+        <v>757054</v>
       </c>
     </row>
     <row r="472" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="B472" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="C472" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="D472" t="s">
-        <v>1112</v>
-      </c>
-      <c r="E472">
-        <v>76245794</v>
+        <v>953</v>
+      </c>
+      <c r="E472" t="s">
+        <v>954</v>
       </c>
       <c r="F472" t="s">
         <v>947</v>
       </c>
-      <c r="G472" t="s">
-        <v>1094</v>
-      </c>
-      <c r="H472">
-        <v>208</v>
+      <c r="G472" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H472" t="s">
+        <v>955</v>
       </c>
       <c r="I472" t="s">
-        <v>1198</v>
-      </c>
-      <c r="J472" t="s">
-        <v>1087</v>
+        <v>956</v>
+      </c>
+      <c r="J472" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K472" t="s">
-        <v>1128</v>
-      </c>
-      <c r="L472" t="s">
-        <v>1128</v>
-      </c>
-      <c r="M472" t="s">
-        <v>1128</v>
-      </c>
-      <c r="N472" t="s">
-        <v>1128</v>
+        <v>1183</v>
+      </c>
+      <c r="L472" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M472" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N472" t="e">
+        <v>#N/A</v>
       </c>
       <c r="O472">
-        <v>762457</v>
+        <v>734894</v>
       </c>
     </row>
     <row r="473" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B473" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="C473" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="D473" t="s">
-        <v>961</v>
-      </c>
-      <c r="E473" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F473" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G473" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H473" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I473" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J473" t="e">
-        <v>#N/A</v>
+        <v>1112</v>
+      </c>
+      <c r="E473">
+        <v>76245794</v>
+      </c>
+      <c r="F473" t="s">
+        <v>947</v>
+      </c>
+      <c r="G473" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H473">
+        <v>208</v>
+      </c>
+      <c r="I473" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J473" t="s">
+        <v>1087</v>
       </c>
       <c r="K473" t="s">
-        <v>1160</v>
+        <v>1128</v>
       </c>
       <c r="L473" t="s">
-        <v>1160</v>
+        <v>1128</v>
       </c>
       <c r="M473" t="s">
-        <v>1160</v>
+        <v>1128</v>
       </c>
       <c r="N473" t="s">
-        <v>1160</v>
-      </c>
-      <c r="O473" t="s">
-        <v>964</v>
+        <v>1128</v>
+      </c>
+      <c r="O473">
+        <v>762457</v>
       </c>
     </row>
     <row r="474" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B474" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="C474" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="D474" t="s">
-        <v>1244</v>
-      </c>
-      <c r="E474">
-        <v>40798937</v>
-      </c>
-      <c r="F474" t="s">
-        <v>947</v>
-      </c>
-      <c r="G474" t="s">
-        <v>1094</v>
-      </c>
-      <c r="H474">
-        <v>5230101</v>
-      </c>
-      <c r="I474" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J474" t="s">
-        <v>1087</v>
+        <v>961</v>
+      </c>
+      <c r="E474" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F474" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G474" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H474" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I474" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J474" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K474" t="s">
         <v>1160</v>
@@ -30680,19 +30722,19 @@
     </row>
     <row r="475" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B475" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="C475" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="D475" t="s">
-        <v>2542</v>
+        <v>1244</v>
       </c>
       <c r="E475">
-        <v>8734202</v>
+        <v>40798937</v>
       </c>
       <c r="F475" t="s">
         <v>947</v>
@@ -30701,45 +30743,45 @@
         <v>1094</v>
       </c>
       <c r="H475">
-        <v>20505</v>
+        <v>5230101</v>
       </c>
       <c r="I475" t="s">
-        <v>1031</v>
+        <v>1245</v>
       </c>
       <c r="J475" t="s">
-        <v>1108</v>
+        <v>1087</v>
       </c>
       <c r="K475" t="s">
-        <v>1114</v>
+        <v>1160</v>
       </c>
       <c r="L475" t="s">
-        <v>2543</v>
+        <v>1160</v>
       </c>
       <c r="M475" t="s">
-        <v>2543</v>
+        <v>1160</v>
       </c>
       <c r="N475" t="s">
-        <v>2543</v>
+        <v>1160</v>
       </c>
       <c r="O475" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
     </row>
     <row r="476" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B476" t="s">
-        <v>2544</v>
+        <v>2541</v>
       </c>
       <c r="C476" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="D476" t="s">
-        <v>2244</v>
+        <v>2542</v>
       </c>
       <c r="E476">
-        <v>71856571</v>
+        <v>8734202</v>
       </c>
       <c r="F476" t="s">
         <v>947</v>
@@ -30748,45 +30790,45 @@
         <v>1094</v>
       </c>
       <c r="H476">
-        <v>1050201</v>
+        <v>20505</v>
       </c>
       <c r="I476" t="s">
-        <v>1120</v>
+        <v>1031</v>
       </c>
       <c r="J476" t="s">
-        <v>1087</v>
+        <v>1108</v>
       </c>
       <c r="K476" t="s">
-        <v>950</v>
+        <v>1114</v>
       </c>
       <c r="L476" t="s">
-        <v>1121</v>
+        <v>2543</v>
       </c>
       <c r="M476" t="s">
-        <v>1122</v>
+        <v>2543</v>
       </c>
       <c r="N476" t="s">
-        <v>1122</v>
+        <v>2543</v>
       </c>
       <c r="O476" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
     </row>
     <row r="477" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B477" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C477" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="D477" t="s">
-        <v>1297</v>
+        <v>2244</v>
       </c>
       <c r="E477">
-        <v>73011197</v>
+        <v>71856571</v>
       </c>
       <c r="F477" t="s">
         <v>947</v>
@@ -30795,45 +30837,45 @@
         <v>1094</v>
       </c>
       <c r="H477">
-        <v>5230101</v>
+        <v>1050201</v>
       </c>
       <c r="I477" t="s">
-        <v>1245</v>
+        <v>1120</v>
       </c>
       <c r="J477" t="s">
         <v>1087</v>
       </c>
       <c r="K477" t="s">
-        <v>1160</v>
+        <v>950</v>
       </c>
       <c r="L477" t="s">
-        <v>1160</v>
+        <v>1121</v>
       </c>
       <c r="M477" t="s">
-        <v>1160</v>
+        <v>1122</v>
       </c>
       <c r="N477" t="s">
-        <v>1160</v>
+        <v>1122</v>
       </c>
       <c r="O477" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
     </row>
     <row r="478" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B478" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C478" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="D478" t="s">
         <v>1297</v>
       </c>
       <c r="E478">
-        <v>72029639</v>
+        <v>73011197</v>
       </c>
       <c r="F478" t="s">
         <v>947</v>
@@ -30863,89 +30905,89 @@
         <v>1160</v>
       </c>
       <c r="O478" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
     </row>
     <row r="479" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="B479" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C479" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="D479" t="s">
-        <v>979</v>
-      </c>
-      <c r="E479" t="s">
-        <v>980</v>
+        <v>1297</v>
+      </c>
+      <c r="E479">
+        <v>72029639</v>
       </c>
       <c r="F479" t="s">
         <v>947</v>
       </c>
-      <c r="G479" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H479" t="s">
-        <v>981</v>
+      <c r="G479" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H479">
+        <v>5230101</v>
       </c>
       <c r="I479" t="s">
-        <v>982</v>
-      </c>
-      <c r="J479" t="e">
-        <v>#N/A</v>
+        <v>1245</v>
+      </c>
+      <c r="J479" t="s">
+        <v>1087</v>
       </c>
       <c r="K479" t="s">
-        <v>1114</v>
-      </c>
-      <c r="L479" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M479" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N479" t="e">
-        <v>#N/A</v>
+        <v>1160</v>
+      </c>
+      <c r="L479" t="s">
+        <v>1160</v>
+      </c>
+      <c r="M479" t="s">
+        <v>1160</v>
+      </c>
+      <c r="N479" t="s">
+        <v>1160</v>
       </c>
       <c r="O479" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
     </row>
     <row r="480" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="B480" t="s">
-        <v>985</v>
+        <v>2547</v>
       </c>
       <c r="C480" t="s">
-        <v>986</v>
+        <v>978</v>
       </c>
       <c r="D480" t="s">
-        <v>987</v>
-      </c>
-      <c r="E480" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F480" t="e">
-        <v>#N/A</v>
+        <v>979</v>
+      </c>
+      <c r="E480" t="s">
+        <v>980</v>
+      </c>
+      <c r="F480" t="s">
+        <v>947</v>
       </c>
       <c r="G480" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H480" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I480" t="e">
-        <v>#N/A</v>
+      <c r="H480" t="s">
+        <v>981</v>
+      </c>
+      <c r="I480" t="s">
+        <v>982</v>
       </c>
       <c r="J480" t="e">
         <v>#N/A</v>
       </c>
       <c r="K480" t="s">
-        <v>1166</v>
+        <v>1114</v>
       </c>
       <c r="L480" t="e">
         <v>#N/A</v>
@@ -30957,118 +30999,118 @@
         <v>#N/A</v>
       </c>
       <c r="O480" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
     </row>
     <row r="481" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>989</v>
+        <v>977</v>
       </c>
       <c r="B481" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="C481" t="s">
-        <v>990</v>
+        <v>2650</v>
       </c>
       <c r="D481" t="s">
-        <v>1297</v>
-      </c>
-      <c r="E481">
-        <v>81353759</v>
+        <v>979</v>
+      </c>
+      <c r="E481" t="s">
+        <v>980</v>
       </c>
       <c r="F481" t="s">
-        <v>1897</v>
-      </c>
-      <c r="G481" t="s">
-        <v>2549</v>
-      </c>
-      <c r="H481">
-        <v>5230102</v>
+        <v>947</v>
+      </c>
+      <c r="G481" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H481" t="s">
+        <v>981</v>
       </c>
       <c r="I481" t="s">
-        <v>2550</v>
-      </c>
-      <c r="J481" t="s">
-        <v>1087</v>
+        <v>982</v>
+      </c>
+      <c r="J481" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K481" t="s">
-        <v>1160</v>
-      </c>
-      <c r="L481" t="s">
-        <v>1160</v>
-      </c>
-      <c r="M481" t="s">
-        <v>1160</v>
-      </c>
-      <c r="N481" t="s">
-        <v>1160</v>
+        <v>1114</v>
+      </c>
+      <c r="L481" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M481" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N481" t="e">
+        <v>#N/A</v>
       </c>
       <c r="O481" t="s">
-        <v>2551</v>
+        <v>983</v>
       </c>
     </row>
     <row r="482" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="B482" t="s">
-        <v>2552</v>
+        <v>985</v>
       </c>
       <c r="C482" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="D482" t="s">
-        <v>2553</v>
-      </c>
-      <c r="E482">
-        <v>41886076</v>
-      </c>
-      <c r="F482" t="s">
-        <v>1897</v>
-      </c>
-      <c r="G482" t="s">
-        <v>2549</v>
-      </c>
-      <c r="H482">
-        <v>5230102</v>
-      </c>
-      <c r="I482" t="s">
-        <v>2550</v>
-      </c>
-      <c r="J482" t="s">
-        <v>1087</v>
+        <v>987</v>
+      </c>
+      <c r="E482" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F482" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G482" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H482" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I482" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J482" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K482" t="s">
-        <v>1160</v>
-      </c>
-      <c r="L482" t="s">
-        <v>1160</v>
-      </c>
-      <c r="M482" t="s">
-        <v>1160</v>
-      </c>
-      <c r="N482" t="s">
-        <v>1160</v>
+        <v>1166</v>
+      </c>
+      <c r="L482" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M482" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N482" t="e">
+        <v>#N/A</v>
       </c>
       <c r="O482" t="s">
-        <v>2554</v>
+        <v>988</v>
       </c>
     </row>
     <row r="483" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="B483" t="s">
-        <v>2555</v>
+        <v>2548</v>
       </c>
       <c r="C483" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="D483" t="s">
-        <v>2035</v>
+        <v>1297</v>
       </c>
       <c r="E483">
-        <v>71742024</v>
+        <v>81353759</v>
       </c>
       <c r="F483" t="s">
         <v>1897</v>
@@ -31077,139 +31119,139 @@
         <v>2549</v>
       </c>
       <c r="H483">
-        <v>1050406</v>
+        <v>5230102</v>
       </c>
       <c r="I483" t="s">
-        <v>1289</v>
+        <v>2550</v>
       </c>
       <c r="J483" t="s">
         <v>1087</v>
       </c>
       <c r="K483" t="s">
-        <v>1183</v>
+        <v>1160</v>
       </c>
       <c r="L483" t="s">
-        <v>1290</v>
+        <v>1160</v>
       </c>
       <c r="M483" t="s">
-        <v>1291</v>
+        <v>1160</v>
       </c>
       <c r="N483" t="s">
-        <v>1291</v>
+        <v>1160</v>
       </c>
       <c r="O483" t="s">
-        <v>2556</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="484" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="B484" t="s">
-        <v>2557</v>
+        <v>2552</v>
       </c>
       <c r="C484" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="D484" t="s">
-        <v>2558</v>
+        <v>2553</v>
       </c>
       <c r="E484">
-        <v>40281119</v>
+        <v>41886076</v>
       </c>
       <c r="F484" t="s">
         <v>1897</v>
       </c>
       <c r="G484" t="s">
-        <v>2559</v>
+        <v>2549</v>
       </c>
       <c r="H484">
-        <v>1030903</v>
+        <v>5230102</v>
       </c>
       <c r="I484" t="s">
-        <v>2560</v>
+        <v>2550</v>
       </c>
       <c r="J484" t="s">
         <v>1087</v>
       </c>
       <c r="K484" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="L484" t="s">
-        <v>1167</v>
+        <v>1160</v>
       </c>
       <c r="M484" t="s">
-        <v>1256</v>
+        <v>1160</v>
       </c>
       <c r="N484" t="s">
-        <v>1256</v>
+        <v>1160</v>
       </c>
       <c r="O484" t="s">
-        <v>2561</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="485" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="B485" t="s">
-        <v>2562</v>
+        <v>2552</v>
       </c>
       <c r="C485" t="s">
-        <v>998</v>
+        <v>2658</v>
       </c>
       <c r="D485" t="s">
-        <v>1330</v>
+        <v>2553</v>
       </c>
       <c r="E485">
-        <v>48707300</v>
+        <v>41886076</v>
       </c>
       <c r="F485" t="s">
         <v>1897</v>
       </c>
       <c r="G485" t="s">
-        <v>2559</v>
+        <v>2549</v>
       </c>
       <c r="H485">
-        <v>1050102</v>
+        <v>5230102</v>
       </c>
       <c r="I485" t="s">
-        <v>2563</v>
+        <v>2550</v>
       </c>
       <c r="J485" t="s">
         <v>1087</v>
       </c>
       <c r="K485" t="s">
-        <v>950</v>
+        <v>1160</v>
       </c>
       <c r="L485" t="s">
-        <v>1315</v>
+        <v>1160</v>
       </c>
       <c r="M485" t="s">
-        <v>1315</v>
+        <v>1160</v>
       </c>
       <c r="N485" t="s">
-        <v>1315</v>
+        <v>1160</v>
       </c>
       <c r="O485" t="s">
-        <v>2564</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="486" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="B486" t="s">
-        <v>2565</v>
+        <v>2555</v>
       </c>
       <c r="C486" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="D486" t="s">
-        <v>1330</v>
+        <v>2035</v>
       </c>
       <c r="E486">
-        <v>46417557</v>
+        <v>71742024</v>
       </c>
       <c r="F486" t="s">
         <v>1897</v>
@@ -31218,292 +31260,292 @@
         <v>2549</v>
       </c>
       <c r="H486">
-        <v>1050102</v>
+        <v>1050406</v>
       </c>
       <c r="I486" t="s">
-        <v>2563</v>
+        <v>1289</v>
       </c>
       <c r="J486" t="s">
         <v>1087</v>
       </c>
       <c r="K486" t="s">
-        <v>950</v>
+        <v>1183</v>
       </c>
       <c r="L486" t="s">
-        <v>1315</v>
+        <v>1290</v>
       </c>
       <c r="M486" t="s">
-        <v>1315</v>
+        <v>1291</v>
       </c>
       <c r="N486" t="s">
-        <v>1315</v>
+        <v>1291</v>
       </c>
       <c r="O486" t="s">
-        <v>2566</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="487" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="B487" t="s">
-        <v>2567</v>
+        <v>2557</v>
       </c>
       <c r="C487" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="D487" t="s">
-        <v>1330</v>
+        <v>2558</v>
       </c>
       <c r="E487">
-        <v>45656769</v>
+        <v>40281119</v>
       </c>
       <c r="F487" t="s">
         <v>1897</v>
       </c>
       <c r="G487" t="s">
-        <v>2549</v>
+        <v>2559</v>
       </c>
       <c r="H487">
-        <v>1050102</v>
+        <v>1030903</v>
       </c>
       <c r="I487" t="s">
-        <v>2563</v>
+        <v>2560</v>
       </c>
       <c r="J487" t="s">
         <v>1087</v>
       </c>
       <c r="K487" t="s">
-        <v>950</v>
+        <v>1166</v>
       </c>
       <c r="L487" t="s">
-        <v>1315</v>
+        <v>1167</v>
       </c>
       <c r="M487" t="s">
-        <v>1315</v>
+        <v>1256</v>
       </c>
       <c r="N487" t="s">
-        <v>1315</v>
+        <v>1256</v>
       </c>
       <c r="O487" t="s">
-        <v>2568</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="488" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="B488" t="s">
-        <v>2569</v>
+        <v>2562</v>
       </c>
       <c r="C488" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="D488" t="s">
-        <v>2570</v>
+        <v>1330</v>
       </c>
       <c r="E488">
-        <v>42092085</v>
+        <v>48707300</v>
       </c>
       <c r="F488" t="s">
         <v>1897</v>
       </c>
       <c r="G488" t="s">
-        <v>2512</v>
+        <v>2559</v>
       </c>
       <c r="H488">
-        <v>3020802</v>
+        <v>1050102</v>
       </c>
       <c r="I488" t="s">
-        <v>2571</v>
+        <v>2563</v>
       </c>
       <c r="J488" t="s">
         <v>1087</v>
       </c>
       <c r="K488" t="s">
-        <v>1102</v>
+        <v>950</v>
       </c>
       <c r="L488" t="s">
-        <v>1173</v>
+        <v>1315</v>
       </c>
       <c r="M488" t="s">
-        <v>2514</v>
+        <v>1315</v>
       </c>
       <c r="N488" t="s">
-        <v>2514</v>
+        <v>1315</v>
       </c>
       <c r="O488" t="s">
-        <v>2572</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="489" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="B489" t="s">
-        <v>2573</v>
+        <v>2565</v>
       </c>
       <c r="C489" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="D489" t="s">
-        <v>2570</v>
+        <v>1330</v>
       </c>
       <c r="E489">
-        <v>46668127</v>
+        <v>46417557</v>
       </c>
       <c r="F489" t="s">
         <v>1897</v>
       </c>
       <c r="G489" t="s">
-        <v>2512</v>
+        <v>2549</v>
       </c>
       <c r="H489">
-        <v>2020104</v>
+        <v>1050102</v>
       </c>
       <c r="I489" t="s">
-        <v>2513</v>
+        <v>2563</v>
       </c>
       <c r="J489" t="s">
         <v>1087</v>
       </c>
       <c r="K489" t="s">
-        <v>1102</v>
+        <v>950</v>
       </c>
       <c r="L489" t="s">
-        <v>1173</v>
+        <v>1315</v>
       </c>
       <c r="M489" t="s">
-        <v>2514</v>
+        <v>1315</v>
       </c>
       <c r="N489" t="s">
-        <v>2514</v>
+        <v>1315</v>
       </c>
       <c r="O489" t="s">
-        <v>2574</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="490" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="B490" t="s">
-        <v>1008</v>
+        <v>2567</v>
       </c>
       <c r="C490" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="D490" t="s">
-        <v>1719</v>
+        <v>1330</v>
       </c>
       <c r="E490">
-        <v>49018949</v>
+        <v>45656769</v>
       </c>
       <c r="F490" t="s">
         <v>1897</v>
       </c>
       <c r="G490" t="s">
-        <v>2575</v>
+        <v>2549</v>
       </c>
       <c r="H490">
-        <v>2020101</v>
+        <v>1050102</v>
       </c>
       <c r="I490" t="s">
-        <v>2576</v>
+        <v>2563</v>
       </c>
       <c r="J490" t="s">
         <v>1087</v>
       </c>
       <c r="K490" t="s">
-        <v>1128</v>
+        <v>950</v>
       </c>
       <c r="L490" t="s">
-        <v>1129</v>
+        <v>1315</v>
       </c>
       <c r="M490" t="s">
-        <v>1130</v>
+        <v>1315</v>
       </c>
       <c r="N490" t="s">
-        <v>2577</v>
+        <v>1315</v>
       </c>
       <c r="O490" t="s">
-        <v>1010</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="491" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>1011</v>
+        <v>1003</v>
       </c>
       <c r="B491" t="s">
-        <v>1008</v>
+        <v>2569</v>
       </c>
       <c r="C491" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="D491" t="s">
-        <v>1719</v>
+        <v>2570</v>
       </c>
       <c r="E491">
-        <v>42234817</v>
+        <v>42092085</v>
       </c>
       <c r="F491" t="s">
         <v>1897</v>
       </c>
       <c r="G491" t="s">
-        <v>2559</v>
+        <v>2512</v>
       </c>
       <c r="H491">
-        <v>2020101</v>
+        <v>3020802</v>
       </c>
       <c r="I491" t="s">
-        <v>2576</v>
+        <v>2571</v>
       </c>
       <c r="J491" t="s">
         <v>1087</v>
       </c>
       <c r="K491" t="s">
-        <v>1128</v>
+        <v>1102</v>
       </c>
       <c r="L491" t="s">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="M491" t="s">
-        <v>1130</v>
+        <v>2514</v>
       </c>
       <c r="N491" t="s">
-        <v>2577</v>
+        <v>2514</v>
       </c>
       <c r="O491" t="s">
-        <v>1010</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="492" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="B492" t="s">
-        <v>1013</v>
+        <v>2573</v>
       </c>
       <c r="C492" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="D492" t="s">
-        <v>1896</v>
+        <v>2570</v>
       </c>
       <c r="E492">
-        <v>30675955</v>
+        <v>46668127</v>
       </c>
       <c r="F492" t="s">
         <v>1897</v>
       </c>
       <c r="G492" t="s">
-        <v>1898</v>
+        <v>2512</v>
       </c>
       <c r="H492">
-        <v>506030101</v>
+        <v>2020104</v>
       </c>
       <c r="I492" t="s">
-        <v>1899</v>
+        <v>2513</v>
       </c>
       <c r="J492" t="s">
         <v>1087</v>
@@ -31515,112 +31557,112 @@
         <v>1173</v>
       </c>
       <c r="M492" t="s">
-        <v>1236</v>
+        <v>2514</v>
       </c>
       <c r="N492" t="s">
-        <v>1900</v>
+        <v>2514</v>
       </c>
       <c r="O492" t="s">
-        <v>1015</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="493" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>1016</v>
+        <v>1007</v>
       </c>
       <c r="B493" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="C493" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="D493" t="s">
-        <v>1233</v>
+        <v>1719</v>
       </c>
       <c r="E493">
-        <v>70837365</v>
+        <v>49018949</v>
       </c>
       <c r="F493" t="s">
         <v>1897</v>
       </c>
       <c r="G493" t="s">
-        <v>1898</v>
+        <v>2575</v>
       </c>
       <c r="H493">
-        <v>506030101</v>
+        <v>2020101</v>
       </c>
       <c r="I493" t="s">
-        <v>1899</v>
+        <v>2576</v>
       </c>
       <c r="J493" t="s">
         <v>1087</v>
       </c>
       <c r="K493" t="s">
-        <v>1102</v>
+        <v>1128</v>
       </c>
       <c r="L493" t="s">
-        <v>1173</v>
+        <v>1129</v>
       </c>
       <c r="M493" t="s">
-        <v>1236</v>
+        <v>1130</v>
       </c>
       <c r="N493" t="s">
-        <v>1900</v>
+        <v>2577</v>
       </c>
       <c r="O493" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="494" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="B494" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="C494" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="D494" t="s">
-        <v>1233</v>
+        <v>1719</v>
       </c>
       <c r="E494">
-        <v>46358832</v>
+        <v>42234817</v>
       </c>
       <c r="F494" t="s">
         <v>1897</v>
       </c>
       <c r="G494" t="s">
-        <v>1898</v>
+        <v>2559</v>
       </c>
       <c r="H494">
-        <v>506030101</v>
+        <v>2020101</v>
       </c>
       <c r="I494" t="s">
-        <v>1899</v>
+        <v>2576</v>
       </c>
       <c r="J494" t="s">
         <v>1087</v>
       </c>
       <c r="K494" t="s">
-        <v>1102</v>
+        <v>1128</v>
       </c>
       <c r="L494" t="s">
-        <v>1173</v>
+        <v>1129</v>
       </c>
       <c r="M494" t="s">
-        <v>1236</v>
+        <v>1130</v>
       </c>
       <c r="N494" t="s">
-        <v>1900</v>
+        <v>2577</v>
       </c>
       <c r="O494" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="495" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="B495" t="s">
         <v>1013</v>
@@ -31629,10 +31671,10 @@
         <v>1014</v>
       </c>
       <c r="D495" t="s">
-        <v>1233</v>
+        <v>1896</v>
       </c>
       <c r="E495">
-        <v>41051834</v>
+        <v>30675955</v>
       </c>
       <c r="F495" t="s">
         <v>1897</v>
@@ -31667,7 +31709,7 @@
     </row>
     <row r="496" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="B496" t="s">
         <v>1013</v>
@@ -31679,7 +31721,7 @@
         <v>1233</v>
       </c>
       <c r="E496">
-        <v>73086539</v>
+        <v>70837365</v>
       </c>
       <c r="F496" t="s">
         <v>1897</v>
@@ -31714,7 +31756,7 @@
     </row>
     <row r="497" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="B497" t="s">
         <v>1013</v>
@@ -31726,7 +31768,7 @@
         <v>1233</v>
       </c>
       <c r="E497">
-        <v>73759137</v>
+        <v>46358832</v>
       </c>
       <c r="F497" t="s">
         <v>1897</v>
@@ -31761,7 +31803,7 @@
     </row>
     <row r="498" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="B498" t="s">
         <v>1013</v>
@@ -31773,7 +31815,7 @@
         <v>1233</v>
       </c>
       <c r="E498">
-        <v>45564265</v>
+        <v>41051834</v>
       </c>
       <c r="F498" t="s">
         <v>1897</v>
@@ -31808,7 +31850,7 @@
     </row>
     <row r="499" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="B499" t="s">
         <v>1013</v>
@@ -31820,7 +31862,7 @@
         <v>1233</v>
       </c>
       <c r="E499">
-        <v>74998492</v>
+        <v>73086539</v>
       </c>
       <c r="F499" t="s">
         <v>1897</v>
@@ -31855,7 +31897,7 @@
     </row>
     <row r="500" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="B500" t="s">
         <v>1013</v>
@@ -31867,7 +31909,7 @@
         <v>1233</v>
       </c>
       <c r="E500">
-        <v>71522935</v>
+        <v>73759137</v>
       </c>
       <c r="F500" t="s">
         <v>1897</v>
@@ -31894,7 +31936,7 @@
         <v>1236</v>
       </c>
       <c r="N500" t="s">
-        <v>1237</v>
+        <v>1900</v>
       </c>
       <c r="O500" t="s">
         <v>1015</v>
@@ -31902,254 +31944,254 @@
     </row>
     <row r="501" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="B501" t="s">
-        <v>2578</v>
+        <v>1013</v>
       </c>
       <c r="C501" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
       <c r="D501" t="s">
-        <v>1758</v>
+        <v>1233</v>
       </c>
       <c r="E501">
-        <v>42782496</v>
+        <v>45564265</v>
       </c>
       <c r="F501" t="s">
         <v>1897</v>
       </c>
       <c r="G501" t="s">
-        <v>2559</v>
+        <v>1898</v>
       </c>
       <c r="H501">
-        <v>103060102</v>
+        <v>506030101</v>
       </c>
       <c r="I501" t="s">
-        <v>2579</v>
+        <v>1899</v>
       </c>
       <c r="J501" t="s">
         <v>1087</v>
       </c>
       <c r="K501" t="s">
-        <v>1183</v>
+        <v>1102</v>
       </c>
       <c r="L501" t="s">
-        <v>1290</v>
+        <v>1173</v>
       </c>
       <c r="M501" t="s">
-        <v>1685</v>
+        <v>1236</v>
       </c>
       <c r="N501" t="s">
-        <v>1685</v>
+        <v>1900</v>
       </c>
       <c r="O501" t="s">
-        <v>2580</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="502" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="B502" t="s">
-        <v>1027</v>
+        <v>1013</v>
       </c>
       <c r="C502" t="s">
-        <v>1028</v>
+        <v>1014</v>
       </c>
       <c r="D502" t="s">
-        <v>1029</v>
+        <v>1233</v>
       </c>
       <c r="E502">
-        <v>47099243</v>
+        <v>74998492</v>
       </c>
       <c r="F502" t="s">
-        <v>947</v>
-      </c>
-      <c r="G502" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H502" t="s">
-        <v>1030</v>
+        <v>1897</v>
+      </c>
+      <c r="G502" t="s">
+        <v>1898</v>
+      </c>
+      <c r="H502">
+        <v>506030101</v>
       </c>
       <c r="I502" t="s">
-        <v>1031</v>
-      </c>
-      <c r="J502" t="e">
-        <v>#N/A</v>
+        <v>1899</v>
+      </c>
+      <c r="J502" t="s">
+        <v>1087</v>
       </c>
       <c r="K502" t="s">
-        <v>1114</v>
-      </c>
-      <c r="L502" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M502" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N502" t="e">
-        <v>#N/A</v>
+        <v>1102</v>
+      </c>
+      <c r="L502" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M502" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N502" t="s">
+        <v>1900</v>
       </c>
       <c r="O502" t="s">
-        <v>2581</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="503" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>1032</v>
+        <v>1023</v>
       </c>
       <c r="B503" t="s">
-        <v>2582</v>
+        <v>1013</v>
       </c>
       <c r="C503" t="s">
-        <v>1033</v>
+        <v>1014</v>
       </c>
       <c r="D503" t="s">
-        <v>2583</v>
+        <v>1233</v>
       </c>
       <c r="E503">
-        <v>2426899</v>
+        <v>71522935</v>
       </c>
       <c r="F503" t="s">
-        <v>1759</v>
+        <v>1897</v>
       </c>
       <c r="G503" t="s">
-        <v>2584</v>
+        <v>1898</v>
       </c>
       <c r="H503">
-        <v>2020301</v>
+        <v>506030101</v>
       </c>
       <c r="I503" t="s">
-        <v>2585</v>
+        <v>1899</v>
       </c>
       <c r="J503" t="s">
         <v>1087</v>
       </c>
       <c r="K503" t="s">
-        <v>1128</v>
+        <v>1102</v>
       </c>
       <c r="L503" t="s">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="M503" t="s">
-        <v>1130</v>
+        <v>1236</v>
       </c>
       <c r="N503" t="s">
-        <v>2168</v>
+        <v>1237</v>
       </c>
       <c r="O503" t="s">
-        <v>2586</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="504" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>1034</v>
+        <v>1024</v>
       </c>
       <c r="B504" t="s">
-        <v>2587</v>
+        <v>2578</v>
       </c>
       <c r="C504" t="s">
-        <v>1035</v>
+        <v>1025</v>
       </c>
       <c r="D504" t="s">
-        <v>2583</v>
+        <v>1758</v>
       </c>
       <c r="E504">
-        <v>29650488</v>
+        <v>42782496</v>
       </c>
       <c r="F504" t="s">
-        <v>1759</v>
+        <v>1897</v>
       </c>
       <c r="G504" t="s">
-        <v>2584</v>
+        <v>2559</v>
       </c>
       <c r="H504">
-        <v>2020301</v>
+        <v>103060102</v>
       </c>
       <c r="I504" t="s">
-        <v>2585</v>
+        <v>2579</v>
       </c>
       <c r="J504" t="s">
         <v>1087</v>
       </c>
       <c r="K504" t="s">
-        <v>1128</v>
+        <v>1183</v>
       </c>
       <c r="L504" t="s">
-        <v>1129</v>
+        <v>1290</v>
       </c>
       <c r="M504" t="s">
-        <v>1130</v>
+        <v>1685</v>
       </c>
       <c r="N504" t="s">
-        <v>2168</v>
+        <v>1685</v>
       </c>
       <c r="O504" t="s">
-        <v>2588</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="505" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>1036</v>
+        <v>1026</v>
       </c>
       <c r="B505" t="s">
-        <v>2589</v>
+        <v>1027</v>
       </c>
       <c r="C505" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
       <c r="D505" t="s">
-        <v>2583</v>
+        <v>1029</v>
       </c>
       <c r="E505">
-        <v>42130766</v>
+        <v>47099243</v>
       </c>
       <c r="F505" t="s">
-        <v>1759</v>
-      </c>
-      <c r="G505" t="s">
-        <v>2584</v>
-      </c>
-      <c r="H505">
-        <v>2020301</v>
+        <v>947</v>
+      </c>
+      <c r="G505" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H505" t="s">
+        <v>1030</v>
       </c>
       <c r="I505" t="s">
-        <v>2585</v>
-      </c>
-      <c r="J505" t="s">
-        <v>1087</v>
+        <v>1031</v>
+      </c>
+      <c r="J505" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K505" t="s">
-        <v>1128</v>
-      </c>
-      <c r="L505" t="s">
-        <v>1129</v>
-      </c>
-      <c r="M505" t="s">
-        <v>1130</v>
-      </c>
-      <c r="N505" t="s">
-        <v>2168</v>
+        <v>1114</v>
+      </c>
+      <c r="L505" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M505" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N505" t="e">
+        <v>#N/A</v>
       </c>
       <c r="O505" t="s">
-        <v>2590</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="506" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="B506" t="s">
-        <v>2591</v>
+        <v>2582</v>
       </c>
       <c r="C506" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="D506" t="s">
         <v>2583</v>
       </c>
       <c r="E506">
-        <v>46459024</v>
+        <v>2426899</v>
       </c>
       <c r="F506" t="s">
         <v>1759</v>
@@ -32179,24 +32221,24 @@
         <v>2168</v>
       </c>
       <c r="O506" t="s">
-        <v>2592</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="507" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="B507" t="s">
-        <v>2593</v>
+        <v>2587</v>
       </c>
       <c r="C507" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="D507" t="s">
         <v>2583</v>
       </c>
       <c r="E507">
-        <v>46667676</v>
+        <v>29650488</v>
       </c>
       <c r="F507" t="s">
         <v>1759</v>
@@ -32226,24 +32268,24 @@
         <v>2168</v>
       </c>
       <c r="O507" t="s">
-        <v>2594</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="508" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="B508" t="s">
-        <v>2595</v>
+        <v>2589</v>
       </c>
       <c r="C508" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="D508" t="s">
         <v>2583</v>
       </c>
       <c r="E508">
-        <v>41921421</v>
+        <v>42130766</v>
       </c>
       <c r="F508" t="s">
         <v>1759</v>
@@ -32273,30 +32315,30 @@
         <v>2168</v>
       </c>
       <c r="O508" t="s">
-        <v>2596</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="509" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="B509" t="s">
-        <v>2597</v>
+        <v>2591</v>
       </c>
       <c r="C509" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="D509" t="s">
         <v>2583</v>
       </c>
       <c r="E509">
-        <v>70894822</v>
+        <v>46459024</v>
       </c>
       <c r="F509" t="s">
         <v>1759</v>
       </c>
       <c r="G509" t="s">
-        <v>2598</v>
+        <v>2584</v>
       </c>
       <c r="H509">
         <v>2020301</v>
@@ -32320,24 +32362,24 @@
         <v>2168</v>
       </c>
       <c r="O509" t="s">
-        <v>2599</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="510" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="B510" t="s">
-        <v>2600</v>
+        <v>2593</v>
       </c>
       <c r="C510" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="D510" t="s">
         <v>2583</v>
       </c>
       <c r="E510">
-        <v>71202943</v>
+        <v>46667676</v>
       </c>
       <c r="F510" t="s">
         <v>1759</v>
@@ -32367,24 +32409,24 @@
         <v>2168</v>
       </c>
       <c r="O510" t="s">
-        <v>2601</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="511" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="B511" t="s">
-        <v>2602</v>
+        <v>2595</v>
       </c>
       <c r="C511" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="D511" t="s">
         <v>2583</v>
       </c>
       <c r="E511">
-        <v>43601505</v>
+        <v>41921421</v>
       </c>
       <c r="F511" t="s">
         <v>1759</v>
@@ -32414,30 +32456,30 @@
         <v>2168</v>
       </c>
       <c r="O511" t="s">
-        <v>2603</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="512" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="B512" t="s">
-        <v>2604</v>
+        <v>2597</v>
       </c>
       <c r="C512" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="D512" t="s">
         <v>2583</v>
       </c>
       <c r="E512">
-        <v>72396792</v>
+        <v>70894822</v>
       </c>
       <c r="F512" t="s">
         <v>1759</v>
       </c>
       <c r="G512" t="s">
-        <v>2584</v>
+        <v>2598</v>
       </c>
       <c r="H512">
         <v>2020301</v>
@@ -32461,24 +32503,24 @@
         <v>2168</v>
       </c>
       <c r="O512" t="s">
-        <v>2605</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="513" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B513" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C513" t="e">
-        <v>#N/A</v>
+        <v>1046</v>
+      </c>
+      <c r="B513" t="s">
+        <v>2600</v>
+      </c>
+      <c r="C513" t="s">
+        <v>1047</v>
       </c>
       <c r="D513" t="s">
-        <v>1719</v>
+        <v>2583</v>
       </c>
       <c r="E513">
-        <v>48349375</v>
+        <v>71202943</v>
       </c>
       <c r="F513" t="s">
         <v>1759</v>
@@ -32508,36 +32550,36 @@
         <v>2168</v>
       </c>
       <c r="O513" t="s">
-        <v>2606</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="514" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="B514" t="s">
-        <v>2607</v>
+        <v>2602</v>
       </c>
       <c r="C514" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="D514" t="s">
-        <v>2608</v>
+        <v>2583</v>
       </c>
       <c r="E514">
-        <v>29315117</v>
+        <v>43601505</v>
       </c>
       <c r="F514" t="s">
         <v>1759</v>
       </c>
       <c r="G514" t="s">
-        <v>1760</v>
+        <v>2584</v>
       </c>
       <c r="H514">
-        <v>2020303</v>
+        <v>2020301</v>
       </c>
       <c r="I514" t="s">
-        <v>2167</v>
+        <v>2585</v>
       </c>
       <c r="J514" t="s">
         <v>1087</v>
@@ -32555,587 +32597,629 @@
         <v>2168</v>
       </c>
       <c r="O514" t="s">
-        <v>2609</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="515" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="B515" t="s">
-        <v>2610</v>
+        <v>2604</v>
       </c>
       <c r="C515" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="D515" t="s">
-        <v>1692</v>
+        <v>2583</v>
       </c>
       <c r="E515">
-        <v>70330624</v>
+        <v>72396792</v>
       </c>
       <c r="F515" t="s">
         <v>1759</v>
       </c>
       <c r="G515" t="s">
-        <v>1760</v>
+        <v>2584</v>
       </c>
       <c r="H515">
-        <v>5230104</v>
+        <v>2020301</v>
       </c>
       <c r="I515" t="s">
-        <v>2611</v>
+        <v>2585</v>
       </c>
       <c r="J515" t="s">
         <v>1087</v>
       </c>
       <c r="K515" t="s">
-        <v>1160</v>
+        <v>1128</v>
       </c>
       <c r="L515" t="s">
-        <v>1160</v>
+        <v>1129</v>
       </c>
       <c r="M515" t="s">
-        <v>1160</v>
+        <v>1130</v>
       </c>
       <c r="N515" t="s">
-        <v>1160</v>
+        <v>2168</v>
       </c>
       <c r="O515" t="s">
-        <v>2612</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="516" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>1057</v>
-      </c>
-      <c r="B516" t="s">
-        <v>2613</v>
-      </c>
-      <c r="C516" t="s">
-        <v>1058</v>
+        <v>1052</v>
+      </c>
+      <c r="B516" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C516" t="e">
+        <v>#N/A</v>
       </c>
       <c r="D516" t="s">
-        <v>1362</v>
+        <v>1719</v>
       </c>
       <c r="E516">
-        <v>43299539</v>
+        <v>48349375</v>
       </c>
       <c r="F516" t="s">
-        <v>1897</v>
+        <v>1759</v>
       </c>
       <c r="G516" t="s">
-        <v>2549</v>
+        <v>2584</v>
       </c>
       <c r="H516">
-        <v>1050202</v>
+        <v>2020301</v>
       </c>
       <c r="I516" t="s">
-        <v>2614</v>
+        <v>2585</v>
       </c>
       <c r="J516" t="s">
         <v>1087</v>
       </c>
       <c r="K516" t="s">
-        <v>950</v>
+        <v>1128</v>
       </c>
       <c r="L516" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="M516" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
       <c r="N516" t="s">
-        <v>1122</v>
+        <v>2168</v>
       </c>
       <c r="O516" t="s">
-        <v>2615</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="517" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="B517" t="s">
-        <v>2616</v>
+        <v>2607</v>
       </c>
       <c r="C517" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="D517" t="s">
-        <v>1334</v>
+        <v>2608</v>
       </c>
       <c r="E517">
-        <v>76328491</v>
+        <v>29315117</v>
       </c>
       <c r="F517" t="s">
-        <v>1897</v>
+        <v>1759</v>
       </c>
       <c r="G517" t="s">
-        <v>2559</v>
+        <v>1760</v>
       </c>
       <c r="H517">
-        <v>1050202</v>
+        <v>2020303</v>
       </c>
       <c r="I517" t="s">
-        <v>2614</v>
+        <v>2167</v>
       </c>
       <c r="J517" t="s">
         <v>1087</v>
       </c>
       <c r="K517" t="s">
-        <v>950</v>
+        <v>1128</v>
       </c>
       <c r="L517" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="M517" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
       <c r="N517" t="s">
-        <v>1122</v>
+        <v>2168</v>
       </c>
       <c r="O517" t="s">
-        <v>2617</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="518" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="B518" t="s">
-        <v>2618</v>
+        <v>2610</v>
       </c>
       <c r="C518" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="D518" t="s">
-        <v>1334</v>
+        <v>1692</v>
       </c>
       <c r="E518">
-        <v>44680031</v>
+        <v>70330624</v>
       </c>
       <c r="F518" t="s">
-        <v>1897</v>
+        <v>1759</v>
       </c>
       <c r="G518" t="s">
-        <v>2559</v>
+        <v>1760</v>
       </c>
       <c r="H518">
-        <v>1050202</v>
+        <v>5230104</v>
       </c>
       <c r="I518" t="s">
-        <v>2614</v>
+        <v>2611</v>
       </c>
       <c r="J518" t="s">
         <v>1087</v>
       </c>
       <c r="K518" t="s">
-        <v>950</v>
+        <v>1160</v>
       </c>
       <c r="L518" t="s">
-        <v>1121</v>
+        <v>1160</v>
       </c>
       <c r="M518" t="s">
-        <v>1122</v>
+        <v>1160</v>
       </c>
       <c r="N518" t="s">
-        <v>1122</v>
+        <v>1160</v>
       </c>
       <c r="O518" t="s">
-        <v>2619</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="519" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="B519" t="s">
-        <v>2620</v>
+        <v>2613</v>
       </c>
       <c r="C519" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="D519" t="s">
-        <v>2621</v>
+        <v>1362</v>
       </c>
       <c r="E519">
-        <v>72134495</v>
+        <v>43299539</v>
       </c>
       <c r="F519" t="s">
         <v>1897</v>
       </c>
       <c r="G519" t="s">
-        <v>2512</v>
+        <v>2549</v>
       </c>
       <c r="H519">
-        <v>506030102</v>
+        <v>1050202</v>
       </c>
       <c r="I519" t="s">
-        <v>2622</v>
+        <v>2614</v>
       </c>
       <c r="J519" t="s">
         <v>1087</v>
       </c>
       <c r="K519" t="s">
-        <v>1102</v>
+        <v>950</v>
       </c>
       <c r="L519" t="s">
-        <v>1173</v>
+        <v>1121</v>
       </c>
       <c r="M519" t="s">
-        <v>1236</v>
+        <v>1122</v>
       </c>
       <c r="N519" t="s">
-        <v>1900</v>
+        <v>1122</v>
       </c>
       <c r="O519" t="s">
-        <v>2623</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="520" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="B520" t="s">
-        <v>2624</v>
+        <v>2616</v>
       </c>
       <c r="C520" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="D520" t="s">
-        <v>2625</v>
+        <v>1334</v>
       </c>
       <c r="E520">
-        <v>45023691</v>
+        <v>76328491</v>
       </c>
       <c r="F520" t="s">
-        <v>947</v>
+        <v>1897</v>
       </c>
       <c r="G520" t="s">
-        <v>1094</v>
+        <v>2559</v>
       </c>
       <c r="H520">
-        <v>20701</v>
+        <v>1050202</v>
       </c>
       <c r="I520" t="s">
-        <v>2131</v>
+        <v>2614</v>
       </c>
       <c r="J520" t="s">
-        <v>1108</v>
+        <v>1087</v>
       </c>
       <c r="K520" t="s">
-        <v>1128</v>
+        <v>950</v>
       </c>
       <c r="L520" t="s">
-        <v>1855</v>
+        <v>1121</v>
       </c>
       <c r="M520" t="s">
-        <v>1856</v>
+        <v>1122</v>
       </c>
       <c r="N520" t="s">
-        <v>1855</v>
+        <v>1122</v>
       </c>
       <c r="O520" t="s">
-        <v>2626</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="521" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="B521" t="s">
-        <v>2627</v>
+        <v>2618</v>
       </c>
       <c r="C521" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="D521" t="s">
-        <v>1084</v>
+        <v>1334</v>
       </c>
       <c r="E521">
-        <v>70546521</v>
+        <v>44680031</v>
       </c>
       <c r="F521" t="s">
-        <v>947</v>
+        <v>1897</v>
       </c>
       <c r="G521" t="s">
-        <v>1429</v>
+        <v>2559</v>
       </c>
       <c r="H521">
-        <v>402030120</v>
+        <v>1050202</v>
       </c>
       <c r="I521" t="s">
-        <v>1430</v>
+        <v>2614</v>
       </c>
       <c r="J521" t="s">
         <v>1087</v>
       </c>
       <c r="K521" t="s">
-        <v>1088</v>
+        <v>950</v>
       </c>
       <c r="L521" t="s">
-        <v>1089</v>
+        <v>1121</v>
       </c>
       <c r="M521" t="s">
-        <v>1431</v>
+        <v>1122</v>
       </c>
       <c r="N521" t="s">
-        <v>1431</v>
+        <v>1122</v>
       </c>
       <c r="O521" t="s">
-        <v>2628</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="522" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="B522" t="s">
-        <v>2629</v>
+        <v>2620</v>
       </c>
       <c r="C522" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D522" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E522" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F522" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G522" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H522" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I522" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J522" t="e">
-        <v>#N/A</v>
+        <v>1064</v>
+      </c>
+      <c r="D522" t="s">
+        <v>2621</v>
+      </c>
+      <c r="E522">
+        <v>72134495</v>
+      </c>
+      <c r="F522" t="s">
+        <v>1897</v>
+      </c>
+      <c r="G522" t="s">
+        <v>2512</v>
+      </c>
+      <c r="H522">
+        <v>506030102</v>
+      </c>
+      <c r="I522" t="s">
+        <v>2622</v>
+      </c>
+      <c r="J522" t="s">
+        <v>1087</v>
       </c>
       <c r="K522" t="s">
-        <v>950</v>
+        <v>1102</v>
       </c>
       <c r="L522" t="s">
-        <v>1436</v>
+        <v>1173</v>
       </c>
       <c r="M522" t="s">
-        <v>1436</v>
+        <v>1236</v>
       </c>
       <c r="N522" t="s">
-        <v>1436</v>
+        <v>1900</v>
+      </c>
+      <c r="O522" t="s">
+        <v>2623</v>
       </c>
     </row>
     <row r="523" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="B523" t="s">
-        <v>2630</v>
+        <v>2624</v>
       </c>
       <c r="C523" t="s">
-        <v>1072</v>
-      </c>
-      <c r="D523" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E523" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F523" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G523" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H523" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I523" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J523" t="e">
-        <v>#N/A</v>
+        <v>1066</v>
+      </c>
+      <c r="D523" t="s">
+        <v>2625</v>
+      </c>
+      <c r="E523">
+        <v>45023691</v>
+      </c>
+      <c r="F523" t="s">
+        <v>947</v>
+      </c>
+      <c r="G523" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H523">
+        <v>20701</v>
+      </c>
+      <c r="I523" t="s">
+        <v>2131</v>
+      </c>
+      <c r="J523" t="s">
+        <v>1108</v>
       </c>
       <c r="K523" t="s">
-        <v>1183</v>
+        <v>1128</v>
       </c>
       <c r="L523" t="s">
-        <v>1184</v>
+        <v>1855</v>
       </c>
       <c r="M523" t="s">
-        <v>2062</v>
+        <v>1856</v>
       </c>
       <c r="N523" t="s">
-        <v>2062</v>
+        <v>1855</v>
+      </c>
+      <c r="O523" t="s">
+        <v>2626</v>
       </c>
     </row>
     <row r="524" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="B524" t="s">
-        <v>2631</v>
+        <v>2627</v>
       </c>
       <c r="C524" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="D524" t="s">
-        <v>1411</v>
+        <v>1084</v>
       </c>
       <c r="E524">
-        <v>41536818</v>
+        <v>70546521</v>
       </c>
       <c r="F524" t="s">
         <v>947</v>
       </c>
       <c r="G524" t="s">
-        <v>1126</v>
+        <v>1429</v>
       </c>
       <c r="H524">
-        <v>201010105</v>
+        <v>402030120</v>
       </c>
       <c r="I524" t="s">
-        <v>1788</v>
+        <v>1430</v>
       </c>
       <c r="J524" t="s">
         <v>1087</v>
       </c>
       <c r="K524" t="s">
-        <v>1128</v>
+        <v>1088</v>
       </c>
       <c r="L524" t="s">
-        <v>1129</v>
+        <v>1089</v>
       </c>
       <c r="M524" t="s">
-        <v>1130</v>
+        <v>1431</v>
       </c>
       <c r="N524" t="s">
-        <v>1131</v>
+        <v>1431</v>
       </c>
       <c r="O524" t="s">
-        <v>2632</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="525" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="B525" t="s">
-        <v>2633</v>
+        <v>2629</v>
       </c>
       <c r="C525" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D525" t="s">
-        <v>2634</v>
-      </c>
-      <c r="E525">
-        <v>29644011</v>
-      </c>
-      <c r="F525" t="s">
-        <v>947</v>
-      </c>
-      <c r="G525" t="s">
-        <v>1094</v>
-      </c>
-      <c r="H525">
-        <v>1030902</v>
-      </c>
-      <c r="I525" t="s">
-        <v>1165</v>
-      </c>
-      <c r="J525" t="s">
-        <v>1087</v>
+        <v>1070</v>
+      </c>
+      <c r="D525" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E525" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F525" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G525" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H525" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I525" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J525" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K525" t="s">
-        <v>1166</v>
+        <v>950</v>
       </c>
       <c r="L525" t="s">
-        <v>1167</v>
+        <v>1436</v>
       </c>
       <c r="M525" t="s">
-        <v>1168</v>
+        <v>1436</v>
       </c>
       <c r="N525" t="s">
-        <v>1168</v>
-      </c>
-      <c r="O525" t="s">
-        <v>2635</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="526" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="B526" t="s">
-        <v>2636</v>
+        <v>2630</v>
       </c>
       <c r="C526" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D526" t="e">
         <v>#N/A</v>
       </c>
-      <c r="E526">
-        <v>70182117</v>
+      <c r="E526" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F526" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G526" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H526" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I526" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J526" t="e">
+        <v>#N/A</v>
       </c>
       <c r="K526" t="s">
-        <v>950</v>
+        <v>1183</v>
       </c>
       <c r="L526" t="s">
-        <v>1121</v>
+        <v>1184</v>
       </c>
       <c r="M526" t="s">
-        <v>1122</v>
+        <v>2062</v>
       </c>
       <c r="N526" t="s">
-        <v>1122</v>
-      </c>
-      <c r="O526" t="s">
-        <v>2637</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="527" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="B527" t="s">
-        <v>2638</v>
+        <v>2631</v>
       </c>
       <c r="C527" t="s">
-        <v>1080</v>
-      </c>
-      <c r="D527" t="e">
-        <v>#N/A</v>
+        <v>1074</v>
+      </c>
+      <c r="D527" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E527">
+        <v>41536818</v>
+      </c>
+      <c r="F527" t="s">
+        <v>947</v>
+      </c>
+      <c r="G527" t="s">
+        <v>1126</v>
+      </c>
+      <c r="H527">
+        <v>201010105</v>
+      </c>
+      <c r="I527" t="s">
+        <v>1788</v>
+      </c>
+      <c r="J527" t="s">
+        <v>1087</v>
       </c>
       <c r="K527" t="s">
-        <v>1166</v>
-      </c>
-      <c r="O527">
-        <v>476903</v>
+        <v>1128</v>
+      </c>
+      <c r="L527" t="s">
+        <v>1129</v>
+      </c>
+      <c r="M527" t="s">
+        <v>1130</v>
+      </c>
+      <c r="N527" t="s">
+        <v>1131</v>
+      </c>
+      <c r="O527" t="s">
+        <v>2632</v>
       </c>
     </row>
     <row r="528" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="B528" t="s">
-        <v>2639</v>
+        <v>2633</v>
       </c>
       <c r="C528" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="D528" t="s">
-        <v>953</v>
+        <v>2634</v>
       </c>
       <c r="E528">
-        <v>72676401</v>
+        <v>29644011</v>
       </c>
       <c r="F528" t="s">
         <v>947</v>
@@ -33144,66 +33228,301 @@
         <v>1094</v>
       </c>
       <c r="H528">
+        <v>1030902</v>
+      </c>
+      <c r="I528" t="s">
+        <v>1165</v>
+      </c>
+      <c r="J528" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K528" t="s">
+        <v>1166</v>
+      </c>
+      <c r="L528" t="s">
+        <v>1167</v>
+      </c>
+      <c r="M528" t="s">
+        <v>1168</v>
+      </c>
+      <c r="N528" t="s">
+        <v>1168</v>
+      </c>
+      <c r="O528" t="s">
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="529" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A529" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B529" t="s">
+        <v>2636</v>
+      </c>
+      <c r="C529" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D529" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E529">
+        <v>70182117</v>
+      </c>
+      <c r="K529" t="s">
+        <v>950</v>
+      </c>
+      <c r="L529" t="s">
+        <v>1121</v>
+      </c>
+      <c r="M529" t="s">
+        <v>1122</v>
+      </c>
+      <c r="N529" t="s">
+        <v>1122</v>
+      </c>
+      <c r="O529" t="s">
+        <v>2637</v>
+      </c>
+    </row>
+    <row r="530" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A530" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B530" t="s">
+        <v>2638</v>
+      </c>
+      <c r="C530" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D530" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K530" t="s">
+        <v>1166</v>
+      </c>
+      <c r="O530">
+        <v>476903</v>
+      </c>
+    </row>
+    <row r="531" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A531" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B531" t="s">
+        <v>2639</v>
+      </c>
+      <c r="C531" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D531" t="s">
+        <v>953</v>
+      </c>
+      <c r="E531">
+        <v>72676401</v>
+      </c>
+      <c r="F531" t="s">
+        <v>947</v>
+      </c>
+      <c r="G531" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H531">
         <v>1031201</v>
       </c>
-      <c r="I528" t="s">
+      <c r="I531" t="s">
         <v>956</v>
       </c>
-      <c r="J528" t="s">
-        <v>1087</v>
-      </c>
-      <c r="K528" t="s">
+      <c r="J531" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K531" t="s">
         <v>1183</v>
       </c>
-      <c r="L528" t="s">
+      <c r="L531" t="s">
         <v>1290</v>
       </c>
-      <c r="M528" t="s">
+      <c r="M531" t="s">
         <v>1445</v>
       </c>
-      <c r="N528" t="s">
+      <c r="N531" t="s">
         <v>1445</v>
       </c>
-      <c r="O528" t="s">
+      <c r="O531" t="s">
         <v>2640</v>
       </c>
     </row>
-    <row r="529" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A529" t="s">
+    <row r="532" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A532" t="s">
         <v>2646</v>
       </c>
-      <c r="B529" t="s">
+      <c r="B532" t="s">
         <v>2642</v>
       </c>
-      <c r="C529" t="s">
+      <c r="C532" t="s">
         <v>2642</v>
       </c>
-      <c r="D529" t="s">
+      <c r="D532" t="s">
         <v>1228</v>
       </c>
-      <c r="F529" t="s">
-        <v>947</v>
-      </c>
-      <c r="G529" t="s">
+      <c r="F532" t="s">
+        <v>947</v>
+      </c>
+      <c r="G532" t="s">
         <v>2643</v>
       </c>
-      <c r="H529" t="s">
+      <c r="H532" t="s">
         <v>2644</v>
       </c>
-      <c r="I529" t="s">
+      <c r="I532" t="s">
         <v>2645</v>
       </c>
-      <c r="K529" t="s">
+      <c r="K532" t="s">
         <v>1102</v>
       </c>
-      <c r="L529" t="s">
+      <c r="L532" t="s">
         <v>1173</v>
       </c>
-      <c r="M529" t="s">
+      <c r="M532" t="s">
         <v>1213</v>
       </c>
-      <c r="N529" t="s">
+      <c r="N532" t="s">
         <v>1213</v>
+      </c>
+    </row>
+    <row r="533" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A533" t="s">
+        <v>2652</v>
+      </c>
+      <c r="B533" t="s">
+        <v>2651</v>
+      </c>
+      <c r="C533" t="s">
+        <v>2651</v>
+      </c>
+      <c r="D533" t="s">
+        <v>1125</v>
+      </c>
+      <c r="K533" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L533" t="s">
+        <v>1129</v>
+      </c>
+      <c r="M533" t="s">
+        <v>1130</v>
+      </c>
+      <c r="N533" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="534" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A534" t="s">
+        <v>2654</v>
+      </c>
+      <c r="B534" t="s">
+        <v>2653</v>
+      </c>
+      <c r="C534" t="s">
+        <v>2653</v>
+      </c>
+      <c r="D534" t="s">
+        <v>1411</v>
+      </c>
+      <c r="K534" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L534" t="s">
+        <v>1129</v>
+      </c>
+      <c r="M534" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="535" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A535" t="s">
+        <v>2656</v>
+      </c>
+      <c r="B535" t="s">
+        <v>2656</v>
+      </c>
+      <c r="C535" t="s">
+        <v>2656</v>
+      </c>
+      <c r="K535" t="s">
+        <v>2655</v>
+      </c>
+      <c r="L535" t="s">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="536" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A536" t="str">
+        <f ca="1">PROPER(Tabla1[[#This Row],[Nombres]])</f>
+        <v>Alexandra Nicole Rosas Lipa</v>
+      </c>
+      <c r="B536" t="s">
+        <v>2657</v>
+      </c>
+      <c r="C536" t="s">
+        <v>2657</v>
+      </c>
+      <c r="D536" t="s">
+        <v>945</v>
+      </c>
+      <c r="K536" t="s">
+        <v>950</v>
+      </c>
+      <c r="L536" t="s">
+        <v>950</v>
+      </c>
+      <c r="M536" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="537" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A537" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B537" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C537" t="s">
+        <v>2661</v>
+      </c>
+      <c r="D537" t="s">
+        <v>2663</v>
+      </c>
+      <c r="K537" t="s">
+        <v>950</v>
+      </c>
+      <c r="L537" t="s">
+        <v>1436</v>
+      </c>
+      <c r="M537" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="538" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A538" t="s">
+        <v>537</v>
+      </c>
+      <c r="B538" t="s">
+        <v>2662</v>
+      </c>
+      <c r="C538" t="s">
+        <v>2662</v>
+      </c>
+      <c r="D538" t="s">
+        <v>1372</v>
+      </c>
+      <c r="K538" t="s">
+        <v>1271</v>
+      </c>
+      <c r="L538" t="s">
+        <v>1271</v>
+      </c>
+      <c r="M538" t="s">
+        <v>1271</v>
       </c>
     </row>
   </sheetData>

--- a/utils/usuarios/USUARIOS_GERENCIAS.xlsx
+++ b/utils/usuarios/USUARIOS_GERENCIAS.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://misiontecnologicasac-my.sharepoint.com/personal/rodrigo_carbonel_misiontecnologica_com/Documents/Documentos/MT-Code/InformeRicoPollo/rico-pollo/utils/usuarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{38C1207D-583A-4E3A-B5BC-FBDCA7AC70E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D15C2AD-0CD7-4B04-91F0-67FEEDA38CA5}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{38C1207D-583A-4E3A-B5BC-FBDCA7AC70E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{393B1C0D-E7EB-4E94-97EB-B83728C38AF2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD6E822C-CF80-4DA1-BFD3-8180C150640C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD6E822C-CF80-4DA1-BFD3-8180C150640C}"/>
   </bookViews>
   <sheets>
     <sheet name="USUARIOS" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6879" uniqueCount="2664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6904" uniqueCount="2675">
   <si>
     <t>Nombres</t>
   </si>
@@ -8031,6 +8031,39 @@
   </si>
   <si>
     <t>COORDINADOR DE PROYECTOS</t>
+  </si>
+  <si>
+    <t>CD JULIACA (COMERCIAL)</t>
+  </si>
+  <si>
+    <t>CD JULIACA (DESPACHO)</t>
+  </si>
+  <si>
+    <t>SAN AGUSTIN</t>
+  </si>
+  <si>
+    <t>CNBRS9X0CB.Planta_de_Alimentos</t>
+  </si>
+  <si>
+    <t>CNBRS9X09M.CD_Juliaca_Comercial</t>
+  </si>
+  <si>
+    <t>CNBRS9X095.CD_Juliaca_Despacho</t>
+  </si>
+  <si>
+    <t>CNBRS9W6Q3.San_Agustín</t>
+  </si>
+  <si>
+    <t>Planta_de_Alimentos</t>
+  </si>
+  <si>
+    <t>CD_Juliaca_Comercial</t>
+  </si>
+  <si>
+    <t>CD_Juliaca_Despacho</t>
+  </si>
+  <si>
+    <t>San_Agustín</t>
   </si>
 </sst>
 </file>
@@ -8086,8 +8119,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{517BEBB2-3A02-4480-8F49-0C1B6B8E7CC2}" name="Tabla1" displayName="Tabla1" ref="A1:O538" totalsRowShown="0">
-  <autoFilter ref="A1:O538" xr:uid="{517BEBB2-3A02-4480-8F49-0C1B6B8E7CC2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{517BEBB2-3A02-4480-8F49-0C1B6B8E7CC2}" name="Tabla1" displayName="Tabla1" ref="A1:O542" totalsRowShown="0">
+  <autoFilter ref="A1:O542" xr:uid="{517BEBB2-3A02-4480-8F49-0C1B6B8E7CC2}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{1F8AA320-CA47-4CCC-8454-28538F97A9FB}" name="Nombres"/>
     <tableColumn id="2" xr3:uid="{DA26F0AB-497D-4C16-8E65-60FDC2ACE02E}" name="Correo"/>
@@ -8426,7 +8459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DD67B1C-CBCD-4893-AAAA-7508CBFE6155}">
-  <dimension ref="A1:O538"/>
+  <dimension ref="A1:O542"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.140625" bestFit="1" customWidth="1"/>
@@ -33456,9 +33489,8 @@
       </c>
     </row>
     <row r="536" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A536" t="str">
-        <f ca="1">PROPER(Tabla1[[#This Row],[Nombres]])</f>
-        <v>Alexandra Nicole Rosas Lipa</v>
+      <c r="A536" t="s">
+        <v>943</v>
       </c>
       <c r="B536" t="s">
         <v>2657</v>
@@ -33523,6 +33555,86 @@
       </c>
       <c r="M538" t="s">
         <v>1271</v>
+      </c>
+    </row>
+    <row r="539" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A539" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B539" t="s">
+        <v>2667</v>
+      </c>
+      <c r="C539" t="s">
+        <v>2667</v>
+      </c>
+      <c r="K539" t="s">
+        <v>1283</v>
+      </c>
+      <c r="L539" t="s">
+        <v>1284</v>
+      </c>
+      <c r="M539" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="540" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A540" t="s">
+        <v>2672</v>
+      </c>
+      <c r="B540" t="s">
+        <v>2668</v>
+      </c>
+      <c r="C540" t="s">
+        <v>2668</v>
+      </c>
+      <c r="K540" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L540" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M540" t="s">
+        <v>2664</v>
+      </c>
+    </row>
+    <row r="541" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A541" t="s">
+        <v>2673</v>
+      </c>
+      <c r="B541" t="s">
+        <v>2669</v>
+      </c>
+      <c r="C541" t="s">
+        <v>2669</v>
+      </c>
+      <c r="K541" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L541" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M541" t="s">
+        <v>2665</v>
+      </c>
+    </row>
+    <row r="542" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A542" t="s">
+        <v>2674</v>
+      </c>
+      <c r="B542" t="s">
+        <v>2670</v>
+      </c>
+      <c r="C542" t="s">
+        <v>2670</v>
+      </c>
+      <c r="K542" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L542" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M542" t="s">
+        <v>2666</v>
       </c>
     </row>
   </sheetData>

--- a/utils/usuarios/USUARIOS_GERENCIAS.xlsx
+++ b/utils/usuarios/USUARIOS_GERENCIAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://misiontecnologicasac-my.sharepoint.com/personal/rodrigo_carbonel_misiontecnologica_com/Documents/Documentos/MT-Code/InformeRicoPollo/rico-pollo/utils/usuarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{38C1207D-583A-4E3A-B5BC-FBDCA7AC70E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{393B1C0D-E7EB-4E94-97EB-B83728C38AF2}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{38C1207D-583A-4E3A-B5BC-FBDCA7AC70E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4DE8BA6-8DB0-451B-80A6-F96C094B7F7C}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD6E822C-CF80-4DA1-BFD3-8180C150640C}"/>
   </bookViews>

--- a/utils/usuarios/USUARIOS_GERENCIAS.xlsx
+++ b/utils/usuarios/USUARIOS_GERENCIAS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://misiontecnologicasac-my.sharepoint.com/personal/rodrigo_carbonel_misiontecnologica_com/Documents/Documentos/MT-Code/InformeRicoPollo/rico-pollo/utils/usuarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{38C1207D-583A-4E3A-B5BC-FBDCA7AC70E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4DE8BA6-8DB0-451B-80A6-F96C094B7F7C}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="8_{38C1207D-583A-4E3A-B5BC-FBDCA7AC70E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11F04EAC-B7EA-43AC-8644-0CF7CC1069CB}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD6E822C-CF80-4DA1-BFD3-8180C150640C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD6E822C-CF80-4DA1-BFD3-8180C150640C}"/>
   </bookViews>
   <sheets>
     <sheet name="USUARIOS" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6904" uniqueCount="2675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7192" uniqueCount="2762">
   <si>
     <t>Nombres</t>
   </si>
@@ -8064,6 +8064,267 @@
   </si>
   <si>
     <t>San_Agustín</t>
+  </si>
+  <si>
+    <t>Pedidos Juliaca</t>
+  </si>
+  <si>
+    <t>Despacho Juliaca</t>
+  </si>
+  <si>
+    <t>Vendedores Juliaca</t>
+  </si>
+  <si>
+    <t>Gina Evelyn Vargas Anconeira</t>
+  </si>
+  <si>
+    <t>Walther Dante Astoquilca Bejar</t>
+  </si>
+  <si>
+    <t>Diego Arnaldo Sanchez Goytendia</t>
+  </si>
+  <si>
+    <t>Esmeralda Humpire Machaca</t>
+  </si>
+  <si>
+    <t>Guido Palomino Huanaeque</t>
+  </si>
+  <si>
+    <t>Marisol Victoria Huayta Puma</t>
+  </si>
+  <si>
+    <t>Jheyson Carlos Montes Condori</t>
+  </si>
+  <si>
+    <t>Calidad Juliaca</t>
+  </si>
+  <si>
+    <t>Cesar Andree Leon Rondon</t>
+  </si>
+  <si>
+    <t>Jose Antonio Alvarez Sumire</t>
+  </si>
+  <si>
+    <t>Eber Villagra Quispe</t>
+  </si>
+  <si>
+    <t>Joel Eduardo Tito Machicado</t>
+  </si>
+  <si>
+    <t>Eder Jossimar Jimenez Huanca</t>
+  </si>
+  <si>
+    <t>Max Robinson Quispe Arizaca</t>
+  </si>
+  <si>
+    <t>Administrator</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>Santiago Arango Velasquez</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Katherin Yessica Tejada Rivera</t>
+  </si>
+  <si>
+    <t>Susan Rouse Portugal Ramos</t>
+  </si>
+  <si>
+    <t>Freddy Alonso Farfan Rodríguez</t>
+  </si>
+  <si>
+    <t>sonia.gutierrez</t>
+  </si>
+  <si>
+    <t>RA</t>
+  </si>
+  <si>
+    <t>TALLER10</t>
+  </si>
+  <si>
+    <t>pedidos.juliaca@ricopollo.pe</t>
+  </si>
+  <si>
+    <t>pedidos.juliaca</t>
+  </si>
+  <si>
+    <t>despacho.juliaca@ricopollo.pe</t>
+  </si>
+  <si>
+    <t>despacho.juliaca</t>
+  </si>
+  <si>
+    <t>vendedores.juliaca@ricopollo.pe</t>
+  </si>
+  <si>
+    <t>vendedores.juliaca</t>
+  </si>
+  <si>
+    <t>gina.vargas@ricopollo.pe</t>
+  </si>
+  <si>
+    <t>gina.vargas</t>
+  </si>
+  <si>
+    <t>wastoquilca@ricopollo.pe</t>
+  </si>
+  <si>
+    <t>wastoquilca</t>
+  </si>
+  <si>
+    <t>dsanchez@ricopollo.pe</t>
+  </si>
+  <si>
+    <t>dsanchez</t>
+  </si>
+  <si>
+    <t>ehumpire@ricopollo.pe</t>
+  </si>
+  <si>
+    <t>ehumpire</t>
+  </si>
+  <si>
+    <t>gpalomino@ricopollo.pe</t>
+  </si>
+  <si>
+    <t>gpalomino</t>
+  </si>
+  <si>
+    <t>marisol.huayta@ricopollo.pe</t>
+  </si>
+  <si>
+    <t>marisol.huayta</t>
+  </si>
+  <si>
+    <t>jheyson.montes@ricopollo.jh</t>
+  </si>
+  <si>
+    <t>jheyson.montes</t>
+  </si>
+  <si>
+    <t>calidad.juliaca@ricopollo.ca</t>
+  </si>
+  <si>
+    <t>calidad.juliaca</t>
+  </si>
+  <si>
+    <t>cleon@ricopollo.cl</t>
+  </si>
+  <si>
+    <t>cleon</t>
+  </si>
+  <si>
+    <t>jalvarez@ricopollo.ja</t>
+  </si>
+  <si>
+    <t>jalvarez</t>
+  </si>
+  <si>
+    <t>eber.villagra@ricopollo.eb</t>
+  </si>
+  <si>
+    <t>eber.villagra</t>
+  </si>
+  <si>
+    <t>jtito@ricopollo.jt</t>
+  </si>
+  <si>
+    <t>jtito</t>
+  </si>
+  <si>
+    <t>eder.jimenez@ricopollo.ed</t>
+  </si>
+  <si>
+    <t>eder.jimenez</t>
+  </si>
+  <si>
+    <t>max.quispe@ricopollo.ma</t>
+  </si>
+  <si>
+    <t>max.quispe</t>
+  </si>
+  <si>
+    <t>Administrator@ricopollo.Ad</t>
+  </si>
+  <si>
+    <t>ST@ricopollo.ST</t>
+  </si>
+  <si>
+    <t>sarango@ricopollo.sa</t>
+  </si>
+  <si>
+    <t>sarango</t>
+  </si>
+  <si>
+    <t>Other@ricopollo.Ot</t>
+  </si>
+  <si>
+    <t>ktejada@ricopollo.kt</t>
+  </si>
+  <si>
+    <t>ktejada</t>
+  </si>
+  <si>
+    <t>sportugal@ricopollo.sp</t>
+  </si>
+  <si>
+    <t>sportugal</t>
+  </si>
+  <si>
+    <t>ffarfan@ricopollo.pe</t>
+  </si>
+  <si>
+    <t>ffarfan</t>
+  </si>
+  <si>
+    <t>sonia.gutierrez@ricopollo.pe</t>
+  </si>
+  <si>
+    <t>RA@ricopollo.RA</t>
+  </si>
+  <si>
+    <t>TALLER10$@ricopollo.TA</t>
+  </si>
+  <si>
+    <t>TALLER10$</t>
+  </si>
+  <si>
+    <t>OPERARIO DE BIOSEGURIDAD</t>
+  </si>
+  <si>
+    <t>REPRODUCCIÓN AVÍCOLA - PRODUCCIÓN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS GG EL ALTO PRODUCCION                                    </t>
+  </si>
+  <si>
+    <t>REPRODUCCIÓN AVÍCOLA</t>
+  </si>
+  <si>
+    <t>ANALISTA DE REPRODUCTORAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADM REPRODUCTORAS                                           </t>
+  </si>
+  <si>
+    <t>ASEGURAMIENTO DE LA CALIDAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIENDAS JULIACA ADM Y SSGG                                  </t>
+  </si>
+  <si>
+    <t>GERENTE DE PLANTA DE EMB. Y PREPARADOS</t>
+  </si>
+  <si>
+    <t>JEFE DE VENTAS</t>
+  </si>
+  <si>
+    <t>EVITAMIENTO OFICINAS</t>
   </si>
 </sst>
 </file>
@@ -8119,8 +8380,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{517BEBB2-3A02-4480-8F49-0C1B6B8E7CC2}" name="Tabla1" displayName="Tabla1" ref="A1:O542" totalsRowShown="0">
-  <autoFilter ref="A1:O542" xr:uid="{517BEBB2-3A02-4480-8F49-0C1B6B8E7CC2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{517BEBB2-3A02-4480-8F49-0C1B6B8E7CC2}" name="Tabla1" displayName="Tabla1" ref="A1:O569" totalsRowShown="0">
+  <autoFilter ref="A1:O569" xr:uid="{517BEBB2-3A02-4480-8F49-0C1B6B8E7CC2}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{1F8AA320-CA47-4CCC-8454-28538F97A9FB}" name="Nombres"/>
     <tableColumn id="2" xr3:uid="{DA26F0AB-497D-4C16-8E65-60FDC2ACE02E}" name="Correo"/>
@@ -8459,7 +8720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DD67B1C-CBCD-4893-AAAA-7508CBFE6155}">
-  <dimension ref="A1:O542"/>
+  <dimension ref="A1:O569"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.140625" bestFit="1" customWidth="1"/>
@@ -8471,7 +8732,8 @@
     <col min="9" max="9" width="13.5703125" customWidth="1"/>
     <col min="10" max="10" width="11.140625" customWidth="1"/>
     <col min="11" max="11" width="60.85546875" customWidth="1"/>
-    <col min="12" max="12" width="49.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="55.5703125" customWidth="1"/>
+    <col min="13" max="13" width="34.42578125" customWidth="1"/>
     <col min="15" max="15" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -33635,6 +33897,1185 @@
       </c>
       <c r="M542" t="s">
         <v>2666</v>
+      </c>
+    </row>
+    <row r="543" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A543" t="s">
+        <v>2675</v>
+      </c>
+      <c r="B543" t="s">
+        <v>2702</v>
+      </c>
+      <c r="C543" t="s">
+        <v>2703</v>
+      </c>
+      <c r="D543" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F543" t="s">
+        <v>1759</v>
+      </c>
+      <c r="G543" t="s">
+        <v>2044</v>
+      </c>
+      <c r="H543">
+        <v>506050101</v>
+      </c>
+      <c r="I543" t="s">
+        <v>2045</v>
+      </c>
+      <c r="J543" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K543" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L543" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M543" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N543" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="544" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A544" t="s">
+        <v>2676</v>
+      </c>
+      <c r="B544" t="s">
+        <v>2704</v>
+      </c>
+      <c r="C544" t="s">
+        <v>2705</v>
+      </c>
+      <c r="F544" t="s">
+        <v>1759</v>
+      </c>
+      <c r="G544" t="s">
+        <v>2044</v>
+      </c>
+      <c r="H544">
+        <v>506050101</v>
+      </c>
+      <c r="I544" t="s">
+        <v>2045</v>
+      </c>
+      <c r="J544" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K544" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L544" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M544" t="s">
+        <v>1236</v>
+      </c>
+      <c r="N544" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="545" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A545" t="s">
+        <v>2677</v>
+      </c>
+      <c r="B545" t="s">
+        <v>2706</v>
+      </c>
+      <c r="C545" t="s">
+        <v>2707</v>
+      </c>
+      <c r="D545" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E545">
+        <v>45386535</v>
+      </c>
+      <c r="F545" t="s">
+        <v>1759</v>
+      </c>
+      <c r="G545" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H545">
+        <v>201010102</v>
+      </c>
+      <c r="I545" t="s">
+        <v>2111</v>
+      </c>
+      <c r="J545" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K545" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L545" t="s">
+        <v>1129</v>
+      </c>
+      <c r="M545" t="s">
+        <v>1130</v>
+      </c>
+      <c r="N545" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="546" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A546" t="s">
+        <v>2678</v>
+      </c>
+      <c r="B546" t="s">
+        <v>2708</v>
+      </c>
+      <c r="C546" t="s">
+        <v>2709</v>
+      </c>
+      <c r="D546" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E546">
+        <v>72758313</v>
+      </c>
+      <c r="F546" t="s">
+        <v>1424</v>
+      </c>
+      <c r="G546" t="s">
+        <v>1303</v>
+      </c>
+      <c r="H546">
+        <v>105040902</v>
+      </c>
+      <c r="I546" t="s">
+        <v>1301</v>
+      </c>
+      <c r="J546" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K546" t="s">
+        <v>1183</v>
+      </c>
+      <c r="L546" t="s">
+        <v>1302</v>
+      </c>
+      <c r="M546" t="s">
+        <v>1303</v>
+      </c>
+      <c r="N546" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="547" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A547" t="s">
+        <v>2679</v>
+      </c>
+      <c r="B547" t="s">
+        <v>2710</v>
+      </c>
+      <c r="C547" t="s">
+        <v>2711</v>
+      </c>
+      <c r="D547" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E547">
+        <v>71457082</v>
+      </c>
+      <c r="F547" t="s">
+        <v>947</v>
+      </c>
+      <c r="G547" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H547">
+        <v>201010112</v>
+      </c>
+      <c r="I547" t="s">
+        <v>1723</v>
+      </c>
+      <c r="J547" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K547" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L547" t="s">
+        <v>1129</v>
+      </c>
+      <c r="M547" t="s">
+        <v>1130</v>
+      </c>
+      <c r="N547" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="548" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A548" t="s">
+        <v>2680</v>
+      </c>
+      <c r="B548" t="s">
+        <v>2712</v>
+      </c>
+      <c r="C548" t="s">
+        <v>2713</v>
+      </c>
+      <c r="D548" t="s">
+        <v>2435</v>
+      </c>
+      <c r="E548">
+        <v>72685618</v>
+      </c>
+      <c r="F548" t="s">
+        <v>947</v>
+      </c>
+      <c r="G548" t="s">
+        <v>1193</v>
+      </c>
+      <c r="H548" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I548" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J548" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K548" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L548" t="s">
+        <v>1192</v>
+      </c>
+      <c r="M548" t="s">
+        <v>1193</v>
+      </c>
+      <c r="N548" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="549" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A549" t="s">
+        <v>2681</v>
+      </c>
+      <c r="B549" t="s">
+        <v>2714</v>
+      </c>
+      <c r="C549" t="s">
+        <v>2715</v>
+      </c>
+      <c r="D549" t="s">
+        <v>2751</v>
+      </c>
+      <c r="E549">
+        <v>70188342</v>
+      </c>
+      <c r="F549" t="s">
+        <v>1424</v>
+      </c>
+      <c r="G549" t="s">
+        <v>2752</v>
+      </c>
+      <c r="H549">
+        <v>402011309</v>
+      </c>
+      <c r="I549" t="s">
+        <v>2753</v>
+      </c>
+      <c r="J549" t="s">
+        <v>1282</v>
+      </c>
+      <c r="K549" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L549" t="s">
+        <v>2754</v>
+      </c>
+      <c r="M549" t="s">
+        <v>2752</v>
+      </c>
+      <c r="N549" t="s">
+        <v>2752</v>
+      </c>
+    </row>
+    <row r="550" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
+        <v>2682</v>
+      </c>
+      <c r="B550" t="s">
+        <v>2716</v>
+      </c>
+      <c r="C550" t="s">
+        <v>2717</v>
+      </c>
+      <c r="D550" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E550">
+        <v>43153545</v>
+      </c>
+      <c r="F550" t="s">
+        <v>947</v>
+      </c>
+      <c r="G550" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H550">
+        <v>201010112</v>
+      </c>
+      <c r="I550" t="s">
+        <v>1723</v>
+      </c>
+      <c r="J550" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K550" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L550" t="s">
+        <v>1129</v>
+      </c>
+      <c r="M550" t="s">
+        <v>1130</v>
+      </c>
+      <c r="N550" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="551" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A551" t="s">
+        <v>2683</v>
+      </c>
+      <c r="B551" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C551" t="s">
+        <v>2719</v>
+      </c>
+      <c r="D551" t="s">
+        <v>2755</v>
+      </c>
+      <c r="E551">
+        <v>45214404</v>
+      </c>
+      <c r="F551" t="s">
+        <v>1424</v>
+      </c>
+      <c r="G551" t="s">
+        <v>2754</v>
+      </c>
+      <c r="H551">
+        <v>4020108</v>
+      </c>
+      <c r="I551" t="s">
+        <v>2756</v>
+      </c>
+      <c r="J551" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K551" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L551" t="s">
+        <v>2754</v>
+      </c>
+      <c r="M551" t="s">
+        <v>2754</v>
+      </c>
+      <c r="N551" t="s">
+        <v>2754</v>
+      </c>
+    </row>
+    <row r="552" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A552" t="s">
+        <v>2684</v>
+      </c>
+      <c r="B552" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C552" t="s">
+        <v>2721</v>
+      </c>
+      <c r="D552" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E552">
+        <v>46894825</v>
+      </c>
+      <c r="F552" t="s">
+        <v>947</v>
+      </c>
+      <c r="G552" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H552">
+        <v>201010116</v>
+      </c>
+      <c r="I552" t="s">
+        <v>1749</v>
+      </c>
+      <c r="J552" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K552" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L552" t="s">
+        <v>1129</v>
+      </c>
+      <c r="M552" t="s">
+        <v>1130</v>
+      </c>
+      <c r="N552" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="553" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A553" t="s">
+        <v>2685</v>
+      </c>
+      <c r="B553" t="s">
+        <v>2722</v>
+      </c>
+      <c r="C553" t="s">
+        <v>2723</v>
+      </c>
+      <c r="D553" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E553" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F553" t="s">
+        <v>1759</v>
+      </c>
+      <c r="G553" t="s">
+        <v>2168</v>
+      </c>
+      <c r="H553">
+        <v>5230104</v>
+      </c>
+      <c r="I553" t="s">
+        <v>2611</v>
+      </c>
+      <c r="J553" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K553" t="s">
+        <v>1114</v>
+      </c>
+      <c r="L553" t="s">
+        <v>2757</v>
+      </c>
+      <c r="M553" t="s">
+        <v>2757</v>
+      </c>
+      <c r="N553" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="554" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A554" t="s">
+        <v>2686</v>
+      </c>
+      <c r="B554" t="s">
+        <v>2724</v>
+      </c>
+      <c r="C554" t="s">
+        <v>2725</v>
+      </c>
+      <c r="D554" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E554">
+        <v>78719941</v>
+      </c>
+      <c r="F554" t="s">
+        <v>947</v>
+      </c>
+      <c r="G554" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H554" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I554" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J554" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K554" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L554" t="s">
+        <v>1129</v>
+      </c>
+      <c r="M554" t="s">
+        <v>1130</v>
+      </c>
+      <c r="N554" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="555" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A555" t="s">
+        <v>2687</v>
+      </c>
+      <c r="B555" t="s">
+        <v>2726</v>
+      </c>
+      <c r="C555" t="s">
+        <v>2727</v>
+      </c>
+      <c r="D555" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E555">
+        <v>29427752</v>
+      </c>
+      <c r="F555" t="s">
+        <v>947</v>
+      </c>
+      <c r="G555" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H555">
+        <v>201010106</v>
+      </c>
+      <c r="I555" t="s">
+        <v>1838</v>
+      </c>
+      <c r="J555" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K555" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L555" t="s">
+        <v>1129</v>
+      </c>
+      <c r="M555" t="s">
+        <v>1130</v>
+      </c>
+      <c r="N555" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="556" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A556" t="s">
+        <v>2688</v>
+      </c>
+      <c r="B556" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C556" t="s">
+        <v>2729</v>
+      </c>
+      <c r="D556" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E556">
+        <v>46235667</v>
+      </c>
+      <c r="F556" t="s">
+        <v>947</v>
+      </c>
+      <c r="G556" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H556">
+        <v>201010115</v>
+      </c>
+      <c r="I556" t="s">
+        <v>1575</v>
+      </c>
+      <c r="J556" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K556" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L556" t="s">
+        <v>1129</v>
+      </c>
+      <c r="M556" t="s">
+        <v>1130</v>
+      </c>
+      <c r="N556" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="557" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A557" t="s">
+        <v>2689</v>
+      </c>
+      <c r="B557" t="s">
+        <v>2730</v>
+      </c>
+      <c r="C557" t="s">
+        <v>2731</v>
+      </c>
+      <c r="D557" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E557">
+        <v>43716590</v>
+      </c>
+      <c r="F557" t="s">
+        <v>947</v>
+      </c>
+      <c r="G557" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H557">
+        <v>201010102</v>
+      </c>
+      <c r="I557" t="s">
+        <v>2111</v>
+      </c>
+      <c r="J557" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K557" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L557" t="s">
+        <v>1129</v>
+      </c>
+      <c r="M557" t="s">
+        <v>1130</v>
+      </c>
+      <c r="N557" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="558" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A558" t="s">
+        <v>2690</v>
+      </c>
+      <c r="B558" t="s">
+        <v>2732</v>
+      </c>
+      <c r="C558" t="s">
+        <v>2733</v>
+      </c>
+      <c r="D558" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E558">
+        <v>45386535</v>
+      </c>
+      <c r="F558" t="s">
+        <v>947</v>
+      </c>
+      <c r="G558" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H558">
+        <v>201010102</v>
+      </c>
+      <c r="I558" t="s">
+        <v>2111</v>
+      </c>
+      <c r="J558" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K558" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L558" t="s">
+        <v>1129</v>
+      </c>
+      <c r="M558" t="s">
+        <v>1130</v>
+      </c>
+      <c r="N558" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="559" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A559" t="s">
+        <v>2691</v>
+      </c>
+      <c r="B559" t="s">
+        <v>2734</v>
+      </c>
+      <c r="C559" t="s">
+        <v>2735</v>
+      </c>
+      <c r="D559" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E559">
+        <v>47119464</v>
+      </c>
+      <c r="F559" t="s">
+        <v>1759</v>
+      </c>
+      <c r="G559" t="s">
+        <v>2168</v>
+      </c>
+      <c r="H559">
+        <v>202030210</v>
+      </c>
+      <c r="I559" t="s">
+        <v>2758</v>
+      </c>
+      <c r="J559" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K559" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L559" t="s">
+        <v>1192</v>
+      </c>
+      <c r="M559" t="s">
+        <v>1193</v>
+      </c>
+      <c r="N559" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="560" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A560" t="s">
+        <v>2692</v>
+      </c>
+      <c r="B560" t="s">
+        <v>2736</v>
+      </c>
+      <c r="C560" t="s">
+        <v>2692</v>
+      </c>
+      <c r="D560" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E560" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F560" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G560" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H560" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I560" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J560" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K560" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L560" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M560" t="s">
+        <v>1128</v>
+      </c>
+      <c r="N560" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="561" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A561" t="s">
+        <v>2693</v>
+      </c>
+      <c r="B561" t="s">
+        <v>2737</v>
+      </c>
+      <c r="C561" t="s">
+        <v>2693</v>
+      </c>
+      <c r="D561" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E561" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F561" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G561" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H561" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I561" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J561" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K561" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L561" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M561" t="s">
+        <v>1128</v>
+      </c>
+      <c r="N561" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="562" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
+        <v>2694</v>
+      </c>
+      <c r="B562" t="s">
+        <v>2738</v>
+      </c>
+      <c r="C562" t="s">
+        <v>2739</v>
+      </c>
+      <c r="D562" t="s">
+        <v>2759</v>
+      </c>
+      <c r="E562">
+        <v>9411833</v>
+      </c>
+      <c r="F562" t="s">
+        <v>947</v>
+      </c>
+      <c r="G562" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H562">
+        <v>50803</v>
+      </c>
+      <c r="I562" t="s">
+        <v>1833</v>
+      </c>
+      <c r="J562" t="s">
+        <v>1108</v>
+      </c>
+      <c r="K562" t="s">
+        <v>1114</v>
+      </c>
+      <c r="L562" t="s">
+        <v>1402</v>
+      </c>
+      <c r="M562" t="s">
+        <v>1402</v>
+      </c>
+      <c r="N562" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="563" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
+        <v>2695</v>
+      </c>
+      <c r="B563" t="s">
+        <v>2740</v>
+      </c>
+      <c r="C563" t="s">
+        <v>2695</v>
+      </c>
+      <c r="D563" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E563" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F563" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G563" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H563" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I563" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J563" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K563" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L563" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M563" t="s">
+        <v>1128</v>
+      </c>
+      <c r="N563" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="564" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
+        <v>2696</v>
+      </c>
+      <c r="B564" t="s">
+        <v>2741</v>
+      </c>
+      <c r="C564" t="s">
+        <v>2742</v>
+      </c>
+      <c r="D564" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E564">
+        <v>75088495</v>
+      </c>
+      <c r="F564" t="s">
+        <v>947</v>
+      </c>
+      <c r="G564" t="s">
+        <v>1291</v>
+      </c>
+      <c r="H564" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I564" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J564" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K564" t="s">
+        <v>1183</v>
+      </c>
+      <c r="L564" t="s">
+        <v>1290</v>
+      </c>
+      <c r="M564" t="s">
+        <v>1291</v>
+      </c>
+      <c r="N564" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="565" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A565" t="s">
+        <v>2697</v>
+      </c>
+      <c r="B565" t="s">
+        <v>2743</v>
+      </c>
+      <c r="C565" t="s">
+        <v>2744</v>
+      </c>
+      <c r="D565" t="s">
+        <v>1679</v>
+      </c>
+      <c r="E565">
+        <v>72522526</v>
+      </c>
+      <c r="F565" t="s">
+        <v>947</v>
+      </c>
+      <c r="G565" t="s">
+        <v>1302</v>
+      </c>
+      <c r="H565">
+        <v>105040909</v>
+      </c>
+      <c r="I565" t="s">
+        <v>2103</v>
+      </c>
+      <c r="J565" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K565" t="s">
+        <v>1183</v>
+      </c>
+      <c r="L565" t="s">
+        <v>1302</v>
+      </c>
+      <c r="M565" t="s">
+        <v>1302</v>
+      </c>
+      <c r="N565" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="566" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A566" t="s">
+        <v>2698</v>
+      </c>
+      <c r="B566" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C566" t="s">
+        <v>2746</v>
+      </c>
+      <c r="D566" t="s">
+        <v>2760</v>
+      </c>
+      <c r="E566">
+        <v>70005456</v>
+      </c>
+      <c r="F566" t="s">
+        <v>947</v>
+      </c>
+      <c r="G566" t="s">
+        <v>2761</v>
+      </c>
+      <c r="H566">
+        <v>20704</v>
+      </c>
+      <c r="I566" t="s">
+        <v>1241</v>
+      </c>
+      <c r="J566" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K566" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L566" t="s">
+        <v>1129</v>
+      </c>
+      <c r="M566" t="s">
+        <v>1130</v>
+      </c>
+      <c r="N566" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="567" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A567" t="s">
+        <v>2699</v>
+      </c>
+      <c r="B567" t="s">
+        <v>2747</v>
+      </c>
+      <c r="C567" t="s">
+        <v>2699</v>
+      </c>
+      <c r="D567" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E567" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F567" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G567" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H567" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I567" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J567" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K567" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L567" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M567" t="s">
+        <v>1128</v>
+      </c>
+      <c r="N567" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="568" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A568" t="s">
+        <v>2700</v>
+      </c>
+      <c r="B568" t="s">
+        <v>2748</v>
+      </c>
+      <c r="C568" t="s">
+        <v>2700</v>
+      </c>
+      <c r="D568" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E568" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F568" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G568" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H568" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I568" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J568" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K568" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L568" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M568" t="s">
+        <v>1128</v>
+      </c>
+      <c r="N568" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="569" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A569" t="s">
+        <v>2701</v>
+      </c>
+      <c r="B569" t="s">
+        <v>2749</v>
+      </c>
+      <c r="C569" t="s">
+        <v>2750</v>
+      </c>
+      <c r="D569" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E569" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F569" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G569" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H569" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I569" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J569" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K569" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L569" t="s">
+        <v>1128</v>
+      </c>
+      <c r="M569" t="s">
+        <v>1128</v>
+      </c>
+      <c r="N569" t="s">
+        <v>1128</v>
       </c>
     </row>
   </sheetData>
